--- a/apps/deep/www/calculators/northeastern-highlands.xlsx
+++ b/apps/deep/www/calculators/northeastern-highlands.xlsx
@@ -16,32 +16,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="curve_key">'Reference'!$A$5:$A$52</definedName>
-    <definedName name="curve_x1">'Reference'!$G$5:$G$52</definedName>
-    <definedName name="curve_y1">'Reference'!$O$5:$O$52</definedName>
-    <definedName name="curve_x2">'Reference'!$H$5:$H$52</definedName>
-    <definedName name="curve_y2">'Reference'!$P$5:$P$52</definedName>
-    <definedName name="curve_x3">'Reference'!$I$5:$I$52</definedName>
-    <definedName name="curve_y3">'Reference'!$Q$5:$Q$52</definedName>
-    <definedName name="curve_x4">'Reference'!$J$5:$J$52</definedName>
-    <definedName name="curve_y4">'Reference'!$R$5:$R$52</definedName>
-    <definedName name="curve_x5">'Reference'!$K$5:$K$52</definedName>
-    <definedName name="curve_y5">'Reference'!$S$5:$S$52</definedName>
-    <definedName name="curve_x6">'Reference'!$L$5:$L$52</definedName>
-    <definedName name="curve_y6">'Reference'!$T$5:$T$52</definedName>
-    <definedName name="curve_x7">'Reference'!$M$5:$M$52</definedName>
-    <definedName name="curve_y7">'Reference'!$U$5:$U$52</definedName>
-    <definedName name="curve_x8">'Reference'!$N$5:$N$52</definedName>
-    <definedName name="curve_y8">'Reference'!$V$5:$V$52</definedName>
-    <definedName name="strata_spring_pctwet2019ws">'Reference'!$A$56:$A$58</definedName>
-    <definedName name="strata_spring_phab_bfwd_rat">'Reference'!$A$59:$A$61</definedName>
-    <definedName name="strata_spring_phab_rp100_cm">'Reference'!$A$62:$A$64</definedName>
-    <definedName name="strata_spring_phab_xbkf_h">'Reference'!$A$65:$A$67</definedName>
-    <definedName name="strata_spring_phab_lrbs_use">'Reference'!$A$68:$A$70</definedName>
-    <definedName name="strata_spring_phab_xcdenmid">'Reference'!$A$71:$A$73</definedName>
-    <definedName name="strata_spring_phab_pct_fast">'Reference'!$A$74:$A$76</definedName>
-    <definedName name="strata_spring_phab_xfc_nat">'Reference'!$A$77:$A$79</definedName>
-    <definedName name="strata_spring_fish_nat_totlntax">'Reference'!$A$80:$A$82</definedName>
+    <definedName name="curve_key">'Reference'!$A$5:$A$53</definedName>
+    <definedName name="curve_x1">'Reference'!$G$5:$G$53</definedName>
+    <definedName name="curve_y1">'Reference'!$O$5:$O$53</definedName>
+    <definedName name="curve_x2">'Reference'!$H$5:$H$53</definedName>
+    <definedName name="curve_y2">'Reference'!$P$5:$P$53</definedName>
+    <definedName name="curve_x3">'Reference'!$I$5:$I$53</definedName>
+    <definedName name="curve_y3">'Reference'!$Q$5:$Q$53</definedName>
+    <definedName name="curve_x4">'Reference'!$J$5:$J$53</definedName>
+    <definedName name="curve_y4">'Reference'!$R$5:$R$53</definedName>
+    <definedName name="curve_x5">'Reference'!$K$5:$K$53</definedName>
+    <definedName name="curve_y5">'Reference'!$S$5:$S$53</definedName>
+    <definedName name="curve_x6">'Reference'!$L$5:$L$53</definedName>
+    <definedName name="curve_y6">'Reference'!$T$5:$T$53</definedName>
+    <definedName name="curve_x7">'Reference'!$M$5:$M$53</definedName>
+    <definedName name="curve_y7">'Reference'!$U$5:$U$53</definedName>
+    <definedName name="curve_x8">'Reference'!$N$5:$N$53</definedName>
+    <definedName name="curve_y8">'Reference'!$V$5:$V$53</definedName>
+    <definedName name="strata_spring_pctwet2019ws">'Reference'!$A$57:$A$59</definedName>
+    <definedName name="strata_spring_phab_bfwd_rat">'Reference'!$A$60:$A$62</definedName>
+    <definedName name="strata_spring_phab_rp100_cm">'Reference'!$A$63:$A$65</definedName>
+    <definedName name="strata_spring_phab_xbkf_h">'Reference'!$A$66:$A$68</definedName>
+    <definedName name="strata_spring_phab_lrbs_use">'Reference'!$A$69:$A$71</definedName>
+    <definedName name="strata_spring_phab_xcdenmid">'Reference'!$A$72:$A$74</definedName>
+    <definedName name="strata_spring_phab_pct_fast">'Reference'!$A$75:$A$77</definedName>
+    <definedName name="strata_spring_phab_xfc_nat">'Reference'!$A$78:$A$80</definedName>
+    <definedName name="strata_spring_fish_nat_totlntax">'Reference'!$A$81:$A$83</definedName>
     <definedName name="idx_spring_pctimp2019ws">'Metrics'!$V$5</definedName>
     <definedName name="idx_spring_pctag2019ws">'Metrics'!$V$6</definedName>
     <definedName name="idx_spring_pctwet2019ws">'Metrics'!$V$7</definedName>
@@ -56,8 +56,8 @@
     <definedName name="idx_spring_phab_sinu">'Metrics'!$V$16</definedName>
     <definedName name="idx_spring_phab_xbka">'Metrics'!$V$17</definedName>
     <definedName name="idx_spring_phab_lrbs_use">'Metrics'!$V$18</definedName>
-    <definedName name="idx_spring_phab_lsub_dmm">'Metrics'!$V$19</definedName>
-    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$20</definedName>
+    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$19</definedName>
+    <definedName name="idx_spring_phab_lsub_dmm">'Metrics'!$V$20</definedName>
     <definedName name="idx_spring_chem_chla">'Metrics'!$V$21</definedName>
     <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$22</definedName>
     <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$23</definedName>
@@ -68,10 +68,11 @@
     <definedName name="idx_spring_chem_turb">'Metrics'!$V$28</definedName>
     <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$29</definedName>
     <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$30</definedName>
-    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$31</definedName>
-    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$32</definedName>
-    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$33</definedName>
-    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$34</definedName>
+    <definedName name="idx_spring_bent_totlntax">'Metrics'!$V$31</definedName>
+    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$32</definedName>
+    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$33</definedName>
+    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$34</definedName>
+    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$35</definedName>
     <definedName name="fs_catchment_hydrology">'Results'!$B$4</definedName>
     <definedName name="fs_surface_water_storage">'Results'!$B$5</definedName>
     <definedName name="fs_reach_inflow">'Results'!$B$6</definedName>
@@ -120,8 +121,8 @@
     <definedName name="in_spring_phab_xbka">'DEEP Score'!$E$29</definedName>
     <definedName name="in_spring_phab_lrbs_use">'DEEP Score'!$E$30</definedName>
     <definedName name="st_spring_phab_lrbs_use">'DEEP Score'!$F$30</definedName>
-    <definedName name="in_spring_phab_lsub_dmm">'DEEP Score'!$E$32</definedName>
-    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$33</definedName>
+    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$32</definedName>
+    <definedName name="in_spring_phab_lsub_dmm">'DEEP Score'!$E$33</definedName>
     <definedName name="in_spring_chem_chla">'DEEP Score'!$E$35</definedName>
     <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$36</definedName>
     <definedName name="st_spring_phab_xcdenmid">'DEEP Score'!$F$36</definedName>
@@ -135,12 +136,13 @@
     <definedName name="st_spring_phab_pct_fast">'DEEP Score'!$F$43</definedName>
     <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$44</definedName>
     <definedName name="st_spring_phab_xfc_nat">'DEEP Score'!$F$44</definedName>
-    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$45</definedName>
-    <definedName name="st_spring_fish_nat_totlntax">'DEEP Score'!$F$45</definedName>
-    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$46</definedName>
-    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$47</definedName>
-    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$48</definedName>
-    <definedName name="site_notes">'DEEP Score'!$A$64</definedName>
+    <definedName name="in_spring_bent_totlntax">'DEEP Score'!$E$45</definedName>
+    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$46</definedName>
+    <definedName name="st_spring_fish_nat_totlntax">'DEEP Score'!$F$46</definedName>
+    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$47</definedName>
+    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$48</definedName>
+    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$49</definedName>
+    <definedName name="site_notes">'DEEP Score'!$A$61</definedName>
     <definedName name="meta_assessment_id">'Metadata'!$B$4</definedName>
     <definedName name="meta_assessment_name">'Metadata'!$B$5</definedName>
     <definedName name="meta_version">'Metadata'!$B$6</definedName>
@@ -720,7 +722,6 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
@@ -752,6 +753,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1561,10 +1563,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 27 curves are fitted to least-disturbed stations of this ecoregion. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
+          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 31 curves are fitted to least-disturbed stations of this ecoregion. 23 of these curves carried forward unchanged from version 8. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1674,7 +1676,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Version 8 | USEPA NRSA 2013-24 (L3 ecoregion 58), StreamCurves regional analysis, methodology 0.13-provisional</t>
+          <t>Version 9 | USEPA NRSA 2013-24 (L3 ecoregion 58), StreamCurves regional analysis, methodology 0.14-provisional</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2415,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Substrate size</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>log mm</t>
+          <t>m3/100m</t>
         </is>
       </c>
       <c r="E32" s="14" t="n"/>
@@ -2441,12 +2443,12 @@
       <c r="B33" s="41" t="n"/>
       <c r="C33" s="42" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Substrate size</t>
         </is>
       </c>
       <c r="D33" s="43" t="inlineStr">
         <is>
-          <t>m3/100m</t>
+          <t>log mm</t>
         </is>
       </c>
       <c r="E33" s="44" t="n"/>
@@ -2786,178 +2788,181 @@
       <c r="I44" s="26" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Population support</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Benthic total taxa richness</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="15" t="inlineStr"/>
+      <c r="G45" s="16">
+        <f>IF('Metrics'!$V$31="","",'Metrics'!$V$31)</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
+        <f>IF('DEEP Score'!$H$45="","",IF('DEEP Score'!$H$45&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$45&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>Native fish taxa richness</t>
         </is>
       </c>
-      <c r="D45" s="30" t="inlineStr"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="32" t="inlineStr">
+      <c r="D46" s="22" t="inlineStr"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="47" t="inlineStr">
         <is>
           <t>All streams (pooled)</t>
         </is>
       </c>
-      <c r="G45" s="33">
-        <f>IF('Metrics'!$V$31="","",'Metrics'!$V$31)</f>
-        <v/>
-      </c>
-      <c r="H45" s="34">
-        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
-        <v/>
-      </c>
-      <c r="I45" s="35">
-        <f>IF('DEEP Score'!$H$45="","",IF('DEEP Score'!$H$45&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$45&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="G46" s="25">
+        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
+        <v/>
+      </c>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="26" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>EPT taxa richness</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="15" t="inlineStr"/>
-      <c r="G46" s="16">
-        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
-        <v/>
-      </c>
-      <c r="H46" s="17">
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="15" t="inlineStr"/>
+      <c r="G47" s="16">
+        <f>IF('Metrics'!$V$33="","",'Metrics'!$V$33)</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
         <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
         <v/>
       </c>
-      <c r="I46" s="18">
-        <f>IF('DEEP Score'!$H$46="","",IF('DEEP Score'!$H$46&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$46&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="n"/>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="I47" s="18">
+        <f>IF('DEEP Score'!$H$47="","",IF('DEEP Score'!$H$47&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$47&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>Shannon diversity (H')</t>
         </is>
       </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="D48" s="22" t="inlineStr">
         <is>
           <t>H'</t>
         </is>
       </c>
-      <c r="E47" s="23" t="n"/>
-      <c r="F47" s="24" t="inlineStr"/>
-      <c r="G47" s="25">
-        <f>IF('Metrics'!$V$33="","",'Metrics'!$V$33)</f>
-        <v/>
-      </c>
-      <c r="H47" s="20" t="n"/>
-      <c r="I47" s="26" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="59" t="inlineStr">
+      <c r="E48" s="23" t="n"/>
+      <c r="F48" s="24" t="inlineStr"/>
+      <c r="G48" s="25">
+        <f>IF('Metrics'!$V$34="","",'Metrics'!$V$34)</f>
+        <v/>
+      </c>
+      <c r="H48" s="20" t="n"/>
+      <c r="I48" s="26" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="D48" s="30" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>dams</t>
         </is>
       </c>
-      <c r="E48" s="31" t="n"/>
-      <c r="F48" s="36" t="inlineStr"/>
-      <c r="G48" s="33">
-        <f>IF('Metrics'!$V$34="","",'Metrics'!$V$34)</f>
-        <v/>
-      </c>
-      <c r="H48" s="34">
+      <c r="E49" s="31" t="n"/>
+      <c r="F49" s="36" t="inlineStr"/>
+      <c r="G49" s="33">
+        <f>IF('Metrics'!$V$35="","",'Metrics'!$V$35)</f>
+        <v/>
+      </c>
+      <c r="H49" s="34">
         <f>IF('Results'!$B$23="","",'Results'!$B$23)</f>
         <v/>
       </c>
-      <c r="I48" s="35">
-        <f>IF('DEEP Score'!$H$48="","",IF('DEEP Score'!$H$48&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$48&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="60" t="inlineStr">
+      <c r="I49" s="35">
+        <f>IF('DEEP Score'!$H$49="","",IF('DEEP Score'!$H$49&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$49&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Sub-index (0 to 1)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="61" t="inlineStr">
-        <is>
-          <t>Physical</t>
-        </is>
-      </c>
-      <c r="B52" s="62">
-        <f>'Results'!$B$26</f>
-        <v/>
-      </c>
-      <c r="C52" s="43">
-        <f>IF('DEEP Score'!$B$52&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$52&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
-        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="61" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="B53" s="62">
-        <f>'Results'!$B$27</f>
+        <f>'Results'!$B$26</f>
         <v/>
       </c>
       <c r="C53" s="43">
@@ -2968,11 +2973,11 @@
     <row r="54">
       <c r="A54" s="61" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="B54" s="62">
-        <f>'Results'!$B$28</f>
+        <f>'Results'!$B$27</f>
         <v/>
       </c>
       <c r="C54" s="43">
@@ -2980,14 +2985,14 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="63" t="inlineStr">
-        <is>
-          <t>Ecosystem Condition Index</t>
-        </is>
-      </c>
-      <c r="B55" s="64">
-        <f>'Results'!$B$29</f>
+    <row r="55">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="B55" s="62">
+        <f>'Results'!$B$28</f>
         <v/>
       </c>
       <c r="C55" s="43">
@@ -2995,143 +3000,129 @@
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Functions with a score: </t>
-        </is>
-      </c>
-      <c r="B56" s="4">
-        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Ecosystem Condition Index</t>
+        </is>
+      </c>
+      <c r="B56" s="64">
+        <f>'Results'!$B$29</f>
+        <v/>
+      </c>
+      <c r="C56" s="43">
+        <f>IF('DEEP Score'!$B$56&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$56&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Functions with a score: </t>
+        </is>
+      </c>
+      <c r="B57" s="4">
+        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="65" t="inlineStr">
-        <is>
-          <t>Withheld for insufficient reference support (not scored)</t>
-        </is>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Tolerant individuals (%) ~ HBI</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Community dynamics</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Benthic total taxa richness</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Population support</t>
-        </is>
-      </c>
+      <c r="A61" s="65" t="n"/>
+      <c r="B61" s="66" t="n"/>
+      <c r="C61" s="66" t="n"/>
+      <c r="D61" s="66" t="n"/>
+      <c r="E61" s="66" t="n"/>
+      <c r="F61" s="66" t="n"/>
+      <c r="G61" s="66" t="n"/>
+      <c r="H61" s="66" t="n"/>
+      <c r="I61" s="67" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="68" t="n"/>
+      <c r="B62" s="69" t="n"/>
+      <c r="C62" s="69" t="n"/>
+      <c r="D62" s="69" t="n"/>
+      <c r="E62" s="69" t="n"/>
+      <c r="F62" s="69" t="n"/>
+      <c r="G62" s="69" t="n"/>
+      <c r="H62" s="69" t="n"/>
+      <c r="I62" s="70" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A63" s="68" t="n"/>
+      <c r="B63" s="69" t="n"/>
+      <c r="C63" s="69" t="n"/>
+      <c r="D63" s="69" t="n"/>
+      <c r="E63" s="69" t="n"/>
+      <c r="F63" s="69" t="n"/>
+      <c r="G63" s="69" t="n"/>
+      <c r="H63" s="69" t="n"/>
+      <c r="I63" s="70" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="66" t="n"/>
-      <c r="B64" s="67" t="n"/>
-      <c r="C64" s="67" t="n"/>
-      <c r="D64" s="67" t="n"/>
-      <c r="E64" s="67" t="n"/>
-      <c r="F64" s="67" t="n"/>
-      <c r="G64" s="67" t="n"/>
-      <c r="H64" s="67" t="n"/>
-      <c r="I64" s="68" t="n"/>
+      <c r="A64" s="68" t="n"/>
+      <c r="B64" s="69" t="n"/>
+      <c r="C64" s="69" t="n"/>
+      <c r="D64" s="69" t="n"/>
+      <c r="E64" s="69" t="n"/>
+      <c r="F64" s="69" t="n"/>
+      <c r="G64" s="69" t="n"/>
+      <c r="H64" s="69" t="n"/>
+      <c r="I64" s="70" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="69" t="n"/>
-      <c r="B65" s="70" t="n"/>
-      <c r="C65" s="70" t="n"/>
-      <c r="D65" s="70" t="n"/>
-      <c r="E65" s="70" t="n"/>
-      <c r="F65" s="70" t="n"/>
-      <c r="G65" s="70" t="n"/>
-      <c r="H65" s="70" t="n"/>
-      <c r="I65" s="71" t="n"/>
+      <c r="A65" s="68" t="n"/>
+      <c r="B65" s="69" t="n"/>
+      <c r="C65" s="69" t="n"/>
+      <c r="D65" s="69" t="n"/>
+      <c r="E65" s="69" t="n"/>
+      <c r="F65" s="69" t="n"/>
+      <c r="G65" s="69" t="n"/>
+      <c r="H65" s="69" t="n"/>
+      <c r="I65" s="70" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="69" t="n"/>
-      <c r="B66" s="70" t="n"/>
-      <c r="C66" s="70" t="n"/>
-      <c r="D66" s="70" t="n"/>
-      <c r="E66" s="70" t="n"/>
-      <c r="F66" s="70" t="n"/>
-      <c r="G66" s="70" t="n"/>
-      <c r="H66" s="70" t="n"/>
-      <c r="I66" s="71" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="69" t="n"/>
-      <c r="B67" s="70" t="n"/>
-      <c r="C67" s="70" t="n"/>
-      <c r="D67" s="70" t="n"/>
-      <c r="E67" s="70" t="n"/>
-      <c r="F67" s="70" t="n"/>
-      <c r="G67" s="70" t="n"/>
-      <c r="H67" s="70" t="n"/>
-      <c r="I67" s="71" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="69" t="n"/>
-      <c r="B68" s="70" t="n"/>
-      <c r="C68" s="70" t="n"/>
-      <c r="D68" s="70" t="n"/>
-      <c r="E68" s="70" t="n"/>
-      <c r="F68" s="70" t="n"/>
-      <c r="G68" s="70" t="n"/>
-      <c r="H68" s="70" t="n"/>
-      <c r="I68" s="71" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="72" t="n"/>
-      <c r="B69" s="73" t="n"/>
-      <c r="C69" s="73" t="n"/>
-      <c r="D69" s="73" t="n"/>
-      <c r="E69" s="73" t="n"/>
-      <c r="F69" s="73" t="n"/>
-      <c r="G69" s="73" t="n"/>
-      <c r="H69" s="73" t="n"/>
-      <c r="I69" s="74" t="n"/>
+      <c r="A66" s="71" t="n"/>
+      <c r="B66" s="72" t="n"/>
+      <c r="C66" s="72" t="n"/>
+      <c r="D66" s="72" t="n"/>
+      <c r="E66" s="72" t="n"/>
+      <c r="F66" s="72" t="n"/>
+      <c r="G66" s="72" t="n"/>
+      <c r="H66" s="72" t="n"/>
+      <c r="I66" s="73" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
-  <mergeCells count="62">
+  <mergeCells count="66">
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I45:I46"/>
     <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B47:B48"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="H38:H39"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B46:B47"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="H32:H34"/>
@@ -3144,12 +3135,12 @@
     <mergeCell ref="H35:H36"/>
     <mergeCell ref="I40:I42"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="I47:I48"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="I12:I13"/>
-    <mergeCell ref="H46:H47"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="H45:H46"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B6:D6"/>
@@ -3157,13 +3148,15 @@
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="A40:A42"/>
     <mergeCell ref="I43:I44"/>
-    <mergeCell ref="A64:I69"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="H47:H48"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="I38:I39"/>
+    <mergeCell ref="A47:A48"/>
     <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A61:I66"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="B18:B20"/>
@@ -3172,6 +3165,7 @@
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="H40:H42"/>
+    <mergeCell ref="B45:B46"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="H30:H31"/>
@@ -3179,11 +3173,10 @@
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B26:B27"/>
-    <mergeCell ref="I46:I47"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="G12:G48">
+  <conditionalFormatting sqref="G12:G49">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(G12),G12&lt;=0.39)</formula>
     </cfRule>
@@ -3194,7 +3187,7 @@
       <formula>AND(ISNUMBER(G12),G12&gt;0.69)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H48">
+  <conditionalFormatting sqref="H12:H49">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(ISNUMBER(H12),H12&lt;=5)</formula>
     </cfRule>
@@ -3205,7 +3198,7 @@
       <formula>AND(ISNUMBER(H12),H12&gt;10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I48">
+  <conditionalFormatting sqref="I12:I49">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>I12="Non-Functioning"</formula>
     </cfRule>
@@ -3241,7 +3234,7 @@
     <dataValidation sqref="F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Curve set" error="Choose a curve set from the list." type="list">
       <formula1>=strata_spring_phab_xfc_nat</formula1>
     </dataValidation>
-    <dataValidation sqref="F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Curve set" error="Choose a curve set from the list." type="list">
+    <dataValidation sqref="F46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Curve set" error="Choose a curve set from the list." type="list">
       <formula1>=strata_spring_fish_nat_totlntax</formula1>
     </dataValidation>
   </dataValidations>
@@ -3256,7 +3249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3265,7 +3258,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Metric indices</t>
         </is>
@@ -3396,87 +3389,87 @@
           <t>Impervious surface</t>
         </is>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="75">
         <f>IF('DEEP Score'!$E$12="","",'DEEP Score'!$E$12)</f>
         <v/>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="75">
         <f>"spring_pctimp2019ws|"&amp;'Metrics'!$C$5</f>
         <v/>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$5,curve_key,0),MATCH("spring_pctimp2019ws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="G5" s="76">
+      <c r="G5" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="K5" s="76">
+      <c r="K5" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="L5" s="76">
+      <c r="L5" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="M5" s="76">
+      <c r="M5" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="N5" s="76">
+      <c r="N5" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="O5" s="76">
+      <c r="O5" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="Q5" s="76">
+      <c r="Q5" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="R5" s="76">
+      <c r="R5" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="S5" s="76">
+      <c r="S5" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="T5" s="76">
+      <c r="T5" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="U5" s="76">
+      <c r="U5" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$5)</f>
         <v/>
       </c>
-      <c r="V5" s="77">
+      <c r="V5" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$5),MAX(0,MIN(1,IF('Metrics'!$B$5&lt;='Metrics'!$F$5,'Metrics'!$N$5,IF('Metrics'!$B$5&gt;='Metrics'!$M$5,'Metrics'!$U$5,IF('Metrics'!$B$5&lt;='Metrics'!$G$5,IF('Metrics'!$G$5-'Metrics'!$F$5&lt;=0,'Metrics'!$O$5,'Metrics'!$N$5+('Metrics'!$B$5-'Metrics'!$F$5)/('Metrics'!$G$5-'Metrics'!$F$5)*('Metrics'!$O$5-'Metrics'!$N$5)),IF('Metrics'!$B$5&lt;='Metrics'!$H$5,IF('Metrics'!$H$5-'Metrics'!$G$5&lt;=0,'Metrics'!$P$5,'Metrics'!$O$5+('Metrics'!$B$5-'Metrics'!$G$5)/('Metrics'!$H$5-'Metrics'!$G$5)*('Metrics'!$P$5-'Metrics'!$O$5)),IF('Metrics'!$B$5&lt;='Metrics'!$I$5,IF('Metrics'!$I$5-'Metrics'!$H$5&lt;=0,'Metrics'!$Q$5,'Metrics'!$P$5+('Metrics'!$B$5-'Metrics'!$H$5)/('Metrics'!$I$5-'Metrics'!$H$5)*('Metrics'!$Q$5-'Metrics'!$P$5)),IF('Metrics'!$B$5&lt;='Metrics'!$J$5,IF('Metrics'!$J$5-'Metrics'!$I$5&lt;=0,'Metrics'!$R$5,'Metrics'!$Q$5+('Metrics'!$B$5-'Metrics'!$I$5)/('Metrics'!$J$5-'Metrics'!$I$5)*('Metrics'!$R$5-'Metrics'!$Q$5)),IF('Metrics'!$B$5&lt;='Metrics'!$K$5,IF('Metrics'!$K$5-'Metrics'!$J$5&lt;=0,'Metrics'!$S$5,'Metrics'!$R$5+('Metrics'!$B$5-'Metrics'!$J$5)/('Metrics'!$K$5-'Metrics'!$J$5)*('Metrics'!$S$5-'Metrics'!$R$5)),IF('Metrics'!$B$5&lt;='Metrics'!$L$5,IF('Metrics'!$L$5-'Metrics'!$K$5&lt;=0,'Metrics'!$T$5,'Metrics'!$S$5+('Metrics'!$B$5-'Metrics'!$K$5)/('Metrics'!$L$5-'Metrics'!$K$5)*('Metrics'!$T$5-'Metrics'!$S$5)),IF('Metrics'!$M$5-'Metrics'!$L$5&lt;=0,'Metrics'!$U$5,'Metrics'!$T$5+('Metrics'!$B$5-'Metrics'!$L$5)/('Metrics'!$M$5-'Metrics'!$L$5)*('Metrics'!$U$5-'Metrics'!$T$5)))))))))))),"")</f>
         <v/>
       </c>
@@ -3487,87 +3480,87 @@
           <t>Agriculture, crop and hay</t>
         </is>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="75">
         <f>IF('DEEP Score'!$E$13="","",'DEEP Score'!$E$13)</f>
         <v/>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="75">
         <f>"spring_pctag2019ws|"&amp;'Metrics'!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$6,curve_key,0),MATCH("spring_pctag2019ws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="K6" s="76">
+      <c r="K6" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="L6" s="76">
+      <c r="L6" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="M6" s="76">
+      <c r="M6" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="N6" s="76">
+      <c r="N6" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="O6" s="76">
+      <c r="O6" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="Q6" s="76">
+      <c r="Q6" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="R6" s="76">
+      <c r="R6" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="S6" s="76">
+      <c r="S6" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="T6" s="76">
+      <c r="T6" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="U6" s="76">
+      <c r="U6" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$6)</f>
         <v/>
       </c>
-      <c r="V6" s="77">
+      <c r="V6" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$6),MAX(0,MIN(1,IF('Metrics'!$B$6&lt;='Metrics'!$F$6,'Metrics'!$N$6,IF('Metrics'!$B$6&gt;='Metrics'!$M$6,'Metrics'!$U$6,IF('Metrics'!$B$6&lt;='Metrics'!$G$6,IF('Metrics'!$G$6-'Metrics'!$F$6&lt;=0,'Metrics'!$O$6,'Metrics'!$N$6+('Metrics'!$B$6-'Metrics'!$F$6)/('Metrics'!$G$6-'Metrics'!$F$6)*('Metrics'!$O$6-'Metrics'!$N$6)),IF('Metrics'!$B$6&lt;='Metrics'!$H$6,IF('Metrics'!$H$6-'Metrics'!$G$6&lt;=0,'Metrics'!$P$6,'Metrics'!$O$6+('Metrics'!$B$6-'Metrics'!$G$6)/('Metrics'!$H$6-'Metrics'!$G$6)*('Metrics'!$P$6-'Metrics'!$O$6)),IF('Metrics'!$B$6&lt;='Metrics'!$I$6,IF('Metrics'!$I$6-'Metrics'!$H$6&lt;=0,'Metrics'!$Q$6,'Metrics'!$P$6+('Metrics'!$B$6-'Metrics'!$H$6)/('Metrics'!$I$6-'Metrics'!$H$6)*('Metrics'!$Q$6-'Metrics'!$P$6)),IF('Metrics'!$B$6&lt;='Metrics'!$J$6,IF('Metrics'!$J$6-'Metrics'!$I$6&lt;=0,'Metrics'!$R$6,'Metrics'!$Q$6+('Metrics'!$B$6-'Metrics'!$I$6)/('Metrics'!$J$6-'Metrics'!$I$6)*('Metrics'!$R$6-'Metrics'!$Q$6)),IF('Metrics'!$B$6&lt;='Metrics'!$K$6,IF('Metrics'!$K$6-'Metrics'!$J$6&lt;=0,'Metrics'!$S$6,'Metrics'!$R$6+('Metrics'!$B$6-'Metrics'!$J$6)/('Metrics'!$K$6-'Metrics'!$J$6)*('Metrics'!$S$6-'Metrics'!$R$6)),IF('Metrics'!$B$6&lt;='Metrics'!$L$6,IF('Metrics'!$L$6-'Metrics'!$K$6&lt;=0,'Metrics'!$T$6,'Metrics'!$S$6+('Metrics'!$B$6-'Metrics'!$K$6)/('Metrics'!$L$6-'Metrics'!$K$6)*('Metrics'!$T$6-'Metrics'!$S$6)),IF('Metrics'!$M$6-'Metrics'!$L$6&lt;=0,'Metrics'!$U$6,'Metrics'!$T$6+('Metrics'!$B$6-'Metrics'!$L$6)/('Metrics'!$M$6-'Metrics'!$L$6)*('Metrics'!$U$6-'Metrics'!$T$6)))))))))))),"")</f>
         <v/>
       </c>
@@ -3578,87 +3571,87 @@
           <t>Wetland</t>
         </is>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="75">
         <f>IF('DEEP Score'!$E$14="","",'DEEP Score'!$E$14)</f>
         <v/>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="75">
         <f>IF('DEEP Score'!$F$14="","All streams (pooled)",'DEEP Score'!$F$14)</f>
         <v/>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="75">
         <f>"spring_pctwet2019ws|"&amp;'Metrics'!$C$7</f>
         <v/>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$7,curve_key,0),MATCH("spring_pctwet2019ws|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="T7" s="76">
+      <c r="T7" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="U7" s="76">
+      <c r="U7" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$7)</f>
         <v/>
       </c>
-      <c r="V7" s="77">
+      <c r="V7" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$7),MAX(0,MIN(1,IF('Metrics'!$B$7&lt;='Metrics'!$F$7,'Metrics'!$N$7,IF('Metrics'!$B$7&gt;='Metrics'!$M$7,'Metrics'!$U$7,IF('Metrics'!$B$7&lt;='Metrics'!$G$7,IF('Metrics'!$G$7-'Metrics'!$F$7&lt;=0,'Metrics'!$O$7,'Metrics'!$N$7+('Metrics'!$B$7-'Metrics'!$F$7)/('Metrics'!$G$7-'Metrics'!$F$7)*('Metrics'!$O$7-'Metrics'!$N$7)),IF('Metrics'!$B$7&lt;='Metrics'!$H$7,IF('Metrics'!$H$7-'Metrics'!$G$7&lt;=0,'Metrics'!$P$7,'Metrics'!$O$7+('Metrics'!$B$7-'Metrics'!$G$7)/('Metrics'!$H$7-'Metrics'!$G$7)*('Metrics'!$P$7-'Metrics'!$O$7)),IF('Metrics'!$B$7&lt;='Metrics'!$I$7,IF('Metrics'!$I$7-'Metrics'!$H$7&lt;=0,'Metrics'!$Q$7,'Metrics'!$P$7+('Metrics'!$B$7-'Metrics'!$H$7)/('Metrics'!$I$7-'Metrics'!$H$7)*('Metrics'!$Q$7-'Metrics'!$P$7)),IF('Metrics'!$B$7&lt;='Metrics'!$J$7,IF('Metrics'!$J$7-'Metrics'!$I$7&lt;=0,'Metrics'!$R$7,'Metrics'!$Q$7+('Metrics'!$B$7-'Metrics'!$I$7)/('Metrics'!$J$7-'Metrics'!$I$7)*('Metrics'!$R$7-'Metrics'!$Q$7)),IF('Metrics'!$B$7&lt;='Metrics'!$K$7,IF('Metrics'!$K$7-'Metrics'!$J$7&lt;=0,'Metrics'!$S$7,'Metrics'!$R$7+('Metrics'!$B$7-'Metrics'!$J$7)/('Metrics'!$K$7-'Metrics'!$J$7)*('Metrics'!$S$7-'Metrics'!$R$7)),IF('Metrics'!$B$7&lt;='Metrics'!$L$7,IF('Metrics'!$L$7-'Metrics'!$K$7&lt;=0,'Metrics'!$T$7,'Metrics'!$S$7+('Metrics'!$B$7-'Metrics'!$K$7)/('Metrics'!$L$7-'Metrics'!$K$7)*('Metrics'!$T$7-'Metrics'!$S$7)),IF('Metrics'!$M$7-'Metrics'!$L$7&lt;=0,'Metrics'!$U$7,'Metrics'!$T$7+('Metrics'!$B$7-'Metrics'!$L$7)/('Metrics'!$M$7-'Metrics'!$L$7)*('Metrics'!$U$7-'Metrics'!$T$7)))))))))))),"")</f>
         <v/>
       </c>
@@ -3669,87 +3662,87 @@
           <t>Road density</t>
         </is>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="75">
         <f>IF('DEEP Score'!$E$15="","",'DEEP Score'!$E$15)</f>
         <v/>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D8" s="76">
+      <c r="D8" s="75">
         <f>"spring_rddensws|"&amp;'Metrics'!$C$8</f>
         <v/>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$8,curve_key,0),MATCH("spring_rddensws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="M8" s="76">
+      <c r="M8" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="Q8" s="76">
+      <c r="Q8" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="S8" s="76">
+      <c r="S8" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="U8" s="76">
+      <c r="U8" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$8)</f>
         <v/>
       </c>
-      <c r="V8" s="77">
+      <c r="V8" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$8),MAX(0,MIN(1,IF('Metrics'!$B$8&lt;='Metrics'!$F$8,'Metrics'!$N$8,IF('Metrics'!$B$8&gt;='Metrics'!$M$8,'Metrics'!$U$8,IF('Metrics'!$B$8&lt;='Metrics'!$G$8,IF('Metrics'!$G$8-'Metrics'!$F$8&lt;=0,'Metrics'!$O$8,'Metrics'!$N$8+('Metrics'!$B$8-'Metrics'!$F$8)/('Metrics'!$G$8-'Metrics'!$F$8)*('Metrics'!$O$8-'Metrics'!$N$8)),IF('Metrics'!$B$8&lt;='Metrics'!$H$8,IF('Metrics'!$H$8-'Metrics'!$G$8&lt;=0,'Metrics'!$P$8,'Metrics'!$O$8+('Metrics'!$B$8-'Metrics'!$G$8)/('Metrics'!$H$8-'Metrics'!$G$8)*('Metrics'!$P$8-'Metrics'!$O$8)),IF('Metrics'!$B$8&lt;='Metrics'!$I$8,IF('Metrics'!$I$8-'Metrics'!$H$8&lt;=0,'Metrics'!$Q$8,'Metrics'!$P$8+('Metrics'!$B$8-'Metrics'!$H$8)/('Metrics'!$I$8-'Metrics'!$H$8)*('Metrics'!$Q$8-'Metrics'!$P$8)),IF('Metrics'!$B$8&lt;='Metrics'!$J$8,IF('Metrics'!$J$8-'Metrics'!$I$8&lt;=0,'Metrics'!$R$8,'Metrics'!$Q$8+('Metrics'!$B$8-'Metrics'!$I$8)/('Metrics'!$J$8-'Metrics'!$I$8)*('Metrics'!$R$8-'Metrics'!$Q$8)),IF('Metrics'!$B$8&lt;='Metrics'!$K$8,IF('Metrics'!$K$8-'Metrics'!$J$8&lt;=0,'Metrics'!$S$8,'Metrics'!$R$8+('Metrics'!$B$8-'Metrics'!$J$8)/('Metrics'!$K$8-'Metrics'!$J$8)*('Metrics'!$S$8-'Metrics'!$R$8)),IF('Metrics'!$B$8&lt;='Metrics'!$L$8,IF('Metrics'!$L$8-'Metrics'!$K$8&lt;=0,'Metrics'!$T$8,'Metrics'!$S$8+('Metrics'!$B$8-'Metrics'!$K$8)/('Metrics'!$L$8-'Metrics'!$K$8)*('Metrics'!$T$8-'Metrics'!$S$8)),IF('Metrics'!$M$8-'Metrics'!$L$8&lt;=0,'Metrics'!$U$8,'Metrics'!$T$8+('Metrics'!$B$8-'Metrics'!$L$8)/('Metrics'!$M$8-'Metrics'!$L$8)*('Metrics'!$U$8-'Metrics'!$T$8)))))))))))),"")</f>
         <v/>
       </c>
@@ -3760,87 +3753,87 @@
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="75">
         <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
         <v/>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="75">
         <f>"spring_bfiws|"&amp;'Metrics'!$C$9</f>
         <v/>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$9,curve_key,0),MATCH("spring_bfiws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="L9" s="76">
+      <c r="L9" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="M9" s="76">
+      <c r="M9" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="N9" s="76">
+      <c r="N9" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="O9" s="76">
+      <c r="O9" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="S9" s="76">
+      <c r="S9" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="T9" s="76">
+      <c r="T9" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="U9" s="76">
+      <c r="U9" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$9)</f>
         <v/>
       </c>
-      <c r="V9" s="77">
+      <c r="V9" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$9),MAX(0,MIN(1,IF('Metrics'!$B$9&lt;='Metrics'!$F$9,'Metrics'!$N$9,IF('Metrics'!$B$9&gt;='Metrics'!$M$9,'Metrics'!$U$9,IF('Metrics'!$B$9&lt;='Metrics'!$G$9,IF('Metrics'!$G$9-'Metrics'!$F$9&lt;=0,'Metrics'!$O$9,'Metrics'!$N$9+('Metrics'!$B$9-'Metrics'!$F$9)/('Metrics'!$G$9-'Metrics'!$F$9)*('Metrics'!$O$9-'Metrics'!$N$9)),IF('Metrics'!$B$9&lt;='Metrics'!$H$9,IF('Metrics'!$H$9-'Metrics'!$G$9&lt;=0,'Metrics'!$P$9,'Metrics'!$O$9+('Metrics'!$B$9-'Metrics'!$G$9)/('Metrics'!$H$9-'Metrics'!$G$9)*('Metrics'!$P$9-'Metrics'!$O$9)),IF('Metrics'!$B$9&lt;='Metrics'!$I$9,IF('Metrics'!$I$9-'Metrics'!$H$9&lt;=0,'Metrics'!$Q$9,'Metrics'!$P$9+('Metrics'!$B$9-'Metrics'!$H$9)/('Metrics'!$I$9-'Metrics'!$H$9)*('Metrics'!$Q$9-'Metrics'!$P$9)),IF('Metrics'!$B$9&lt;='Metrics'!$J$9,IF('Metrics'!$J$9-'Metrics'!$I$9&lt;=0,'Metrics'!$R$9,'Metrics'!$Q$9+('Metrics'!$B$9-'Metrics'!$I$9)/('Metrics'!$J$9-'Metrics'!$I$9)*('Metrics'!$R$9-'Metrics'!$Q$9)),IF('Metrics'!$B$9&lt;='Metrics'!$K$9,IF('Metrics'!$K$9-'Metrics'!$J$9&lt;=0,'Metrics'!$S$9,'Metrics'!$R$9+('Metrics'!$B$9-'Metrics'!$J$9)/('Metrics'!$K$9-'Metrics'!$J$9)*('Metrics'!$S$9-'Metrics'!$R$9)),IF('Metrics'!$B$9&lt;='Metrics'!$L$9,IF('Metrics'!$L$9-'Metrics'!$K$9&lt;=0,'Metrics'!$T$9,'Metrics'!$S$9+('Metrics'!$B$9-'Metrics'!$K$9)/('Metrics'!$L$9-'Metrics'!$K$9)*('Metrics'!$T$9-'Metrics'!$S$9)),IF('Metrics'!$M$9-'Metrics'!$L$9&lt;=0,'Metrics'!$U$9,'Metrics'!$T$9+('Metrics'!$B$9-'Metrics'!$L$9)/('Metrics'!$M$9-'Metrics'!$L$9)*('Metrics'!$U$9-'Metrics'!$T$9)))))))))))),"")</f>
         <v/>
       </c>
@@ -3851,87 +3844,87 @@
           <t>Degree of regulation</t>
         </is>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="75">
         <f>IF('DEEP Score'!$E$17="","",'DEEP Score'!$E$17)</f>
         <v/>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="75">
         <f>"spring_dorws|"&amp;'Metrics'!$C$10</f>
         <v/>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$10,curve_key,0),MATCH("spring_dorws|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="I10" s="76">
+      <c r="I10" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="L10" s="76">
+      <c r="L10" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="M10" s="76">
+      <c r="M10" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="N10" s="76">
+      <c r="N10" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="O10" s="76">
+      <c r="O10" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="P10" s="76">
+      <c r="P10" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="Q10" s="76">
+      <c r="Q10" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="R10" s="76">
+      <c r="R10" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="S10" s="76">
+      <c r="S10" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="T10" s="76">
+      <c r="T10" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="U10" s="76">
+      <c r="U10" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$10)</f>
         <v/>
       </c>
-      <c r="V10" s="77">
+      <c r="V10" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$10),MAX(0,MIN(1,IF('Metrics'!$B$10&lt;='Metrics'!$F$10,'Metrics'!$N$10,IF('Metrics'!$B$10&gt;='Metrics'!$M$10,'Metrics'!$U$10,IF('Metrics'!$B$10&lt;='Metrics'!$G$10,IF('Metrics'!$G$10-'Metrics'!$F$10&lt;=0,'Metrics'!$O$10,'Metrics'!$N$10+('Metrics'!$B$10-'Metrics'!$F$10)/('Metrics'!$G$10-'Metrics'!$F$10)*('Metrics'!$O$10-'Metrics'!$N$10)),IF('Metrics'!$B$10&lt;='Metrics'!$H$10,IF('Metrics'!$H$10-'Metrics'!$G$10&lt;=0,'Metrics'!$P$10,'Metrics'!$O$10+('Metrics'!$B$10-'Metrics'!$G$10)/('Metrics'!$H$10-'Metrics'!$G$10)*('Metrics'!$P$10-'Metrics'!$O$10)),IF('Metrics'!$B$10&lt;='Metrics'!$I$10,IF('Metrics'!$I$10-'Metrics'!$H$10&lt;=0,'Metrics'!$Q$10,'Metrics'!$P$10+('Metrics'!$B$10-'Metrics'!$H$10)/('Metrics'!$I$10-'Metrics'!$H$10)*('Metrics'!$Q$10-'Metrics'!$P$10)),IF('Metrics'!$B$10&lt;='Metrics'!$J$10,IF('Metrics'!$J$10-'Metrics'!$I$10&lt;=0,'Metrics'!$R$10,'Metrics'!$Q$10+('Metrics'!$B$10-'Metrics'!$I$10)/('Metrics'!$J$10-'Metrics'!$I$10)*('Metrics'!$R$10-'Metrics'!$Q$10)),IF('Metrics'!$B$10&lt;='Metrics'!$K$10,IF('Metrics'!$K$10-'Metrics'!$J$10&lt;=0,'Metrics'!$S$10,'Metrics'!$R$10+('Metrics'!$B$10-'Metrics'!$J$10)/('Metrics'!$K$10-'Metrics'!$J$10)*('Metrics'!$S$10-'Metrics'!$R$10)),IF('Metrics'!$B$10&lt;='Metrics'!$L$10,IF('Metrics'!$L$10-'Metrics'!$K$10&lt;=0,'Metrics'!$T$10,'Metrics'!$S$10+('Metrics'!$B$10-'Metrics'!$K$10)/('Metrics'!$L$10-'Metrics'!$K$10)*('Metrics'!$T$10-'Metrics'!$S$10)),IF('Metrics'!$M$10-'Metrics'!$L$10&lt;=0,'Metrics'!$U$10,'Metrics'!$T$10+('Metrics'!$B$10-'Metrics'!$L$10)/('Metrics'!$M$10-'Metrics'!$L$10)*('Metrics'!$U$10-'Metrics'!$T$10)))))))))))),"")</f>
         <v/>
       </c>
@@ -3942,87 +3935,87 @@
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="75">
         <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
         <v/>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="75">
         <f>IF('DEEP Score'!$F$19="","All streams (pooled)",'DEEP Score'!$F$19)</f>
         <v/>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="75">
         <f>"spring_phab_bfwd_rat|"&amp;'Metrics'!$C$11</f>
         <v/>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$11,curve_key,0),MATCH("spring_phab_bfwd_rat|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="G11" s="76">
+      <c r="G11" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="H11" s="76">
+      <c r="H11" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="I11" s="76">
+      <c r="I11" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="L11" s="76">
+      <c r="L11" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="M11" s="76">
+      <c r="M11" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="N11" s="76">
+      <c r="N11" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="O11" s="76">
+      <c r="O11" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="R11" s="76">
+      <c r="R11" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="S11" s="76">
+      <c r="S11" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="T11" s="76">
+      <c r="T11" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="U11" s="76">
+      <c r="U11" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$11)</f>
         <v/>
       </c>
-      <c r="V11" s="77">
+      <c r="V11" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$11),MAX(0,MIN(1,IF('Metrics'!$B$11&lt;='Metrics'!$F$11,'Metrics'!$N$11,IF('Metrics'!$B$11&gt;='Metrics'!$M$11,'Metrics'!$U$11,IF('Metrics'!$B$11&lt;='Metrics'!$G$11,IF('Metrics'!$G$11-'Metrics'!$F$11&lt;=0,'Metrics'!$O$11,'Metrics'!$N$11+('Metrics'!$B$11-'Metrics'!$F$11)/('Metrics'!$G$11-'Metrics'!$F$11)*('Metrics'!$O$11-'Metrics'!$N$11)),IF('Metrics'!$B$11&lt;='Metrics'!$H$11,IF('Metrics'!$H$11-'Metrics'!$G$11&lt;=0,'Metrics'!$P$11,'Metrics'!$O$11+('Metrics'!$B$11-'Metrics'!$G$11)/('Metrics'!$H$11-'Metrics'!$G$11)*('Metrics'!$P$11-'Metrics'!$O$11)),IF('Metrics'!$B$11&lt;='Metrics'!$I$11,IF('Metrics'!$I$11-'Metrics'!$H$11&lt;=0,'Metrics'!$Q$11,'Metrics'!$P$11+('Metrics'!$B$11-'Metrics'!$H$11)/('Metrics'!$I$11-'Metrics'!$H$11)*('Metrics'!$Q$11-'Metrics'!$P$11)),IF('Metrics'!$B$11&lt;='Metrics'!$J$11,IF('Metrics'!$J$11-'Metrics'!$I$11&lt;=0,'Metrics'!$R$11,'Metrics'!$Q$11+('Metrics'!$B$11-'Metrics'!$I$11)/('Metrics'!$J$11-'Metrics'!$I$11)*('Metrics'!$R$11-'Metrics'!$Q$11)),IF('Metrics'!$B$11&lt;='Metrics'!$K$11,IF('Metrics'!$K$11-'Metrics'!$J$11&lt;=0,'Metrics'!$S$11,'Metrics'!$R$11+('Metrics'!$B$11-'Metrics'!$J$11)/('Metrics'!$K$11-'Metrics'!$J$11)*('Metrics'!$S$11-'Metrics'!$R$11)),IF('Metrics'!$B$11&lt;='Metrics'!$L$11,IF('Metrics'!$L$11-'Metrics'!$K$11&lt;=0,'Metrics'!$T$11,'Metrics'!$S$11+('Metrics'!$B$11-'Metrics'!$K$11)/('Metrics'!$L$11-'Metrics'!$K$11)*('Metrics'!$T$11-'Metrics'!$S$11)),IF('Metrics'!$M$11-'Metrics'!$L$11&lt;=0,'Metrics'!$U$11,'Metrics'!$T$11+('Metrics'!$B$11-'Metrics'!$L$11)/('Metrics'!$M$11-'Metrics'!$L$11)*('Metrics'!$U$11-'Metrics'!$T$11)))))))))))),"")</f>
         <v/>
       </c>
@@ -4033,87 +4026,87 @@
           <t>Residual pool depth</t>
         </is>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="75">
         <f>IF('DEEP Score'!$E$20="","",'DEEP Score'!$E$20)</f>
         <v/>
       </c>
-      <c r="C12" s="76">
+      <c r="C12" s="75">
         <f>IF('DEEP Score'!$F$20="","All streams (pooled)",'DEEP Score'!$F$20)</f>
         <v/>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="75">
         <f>"spring_phab_rp100_cm|"&amp;'Metrics'!$C$12</f>
         <v/>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$12,curve_key,0),MATCH("spring_phab_rp100_cm|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F12" s="76">
+      <c r="F12" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="G12" s="76">
+      <c r="G12" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="I12" s="76">
+      <c r="I12" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="L12" s="76">
+      <c r="L12" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="M12" s="76">
+      <c r="M12" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="N12" s="76">
+      <c r="N12" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="O12" s="76">
+      <c r="O12" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="Q12" s="76">
+      <c r="Q12" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="R12" s="76">
+      <c r="R12" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="S12" s="76">
+      <c r="S12" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="T12" s="76">
+      <c r="T12" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="U12" s="76">
+      <c r="U12" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$12)</f>
         <v/>
       </c>
-      <c r="V12" s="77">
+      <c r="V12" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$12),MAX(0,MIN(1,IF('Metrics'!$B$12&lt;='Metrics'!$F$12,'Metrics'!$N$12,IF('Metrics'!$B$12&gt;='Metrics'!$M$12,'Metrics'!$U$12,IF('Metrics'!$B$12&lt;='Metrics'!$G$12,IF('Metrics'!$G$12-'Metrics'!$F$12&lt;=0,'Metrics'!$O$12,'Metrics'!$N$12+('Metrics'!$B$12-'Metrics'!$F$12)/('Metrics'!$G$12-'Metrics'!$F$12)*('Metrics'!$O$12-'Metrics'!$N$12)),IF('Metrics'!$B$12&lt;='Metrics'!$H$12,IF('Metrics'!$H$12-'Metrics'!$G$12&lt;=0,'Metrics'!$P$12,'Metrics'!$O$12+('Metrics'!$B$12-'Metrics'!$G$12)/('Metrics'!$H$12-'Metrics'!$G$12)*('Metrics'!$P$12-'Metrics'!$O$12)),IF('Metrics'!$B$12&lt;='Metrics'!$I$12,IF('Metrics'!$I$12-'Metrics'!$H$12&lt;=0,'Metrics'!$Q$12,'Metrics'!$P$12+('Metrics'!$B$12-'Metrics'!$H$12)/('Metrics'!$I$12-'Metrics'!$H$12)*('Metrics'!$Q$12-'Metrics'!$P$12)),IF('Metrics'!$B$12&lt;='Metrics'!$J$12,IF('Metrics'!$J$12-'Metrics'!$I$12&lt;=0,'Metrics'!$R$12,'Metrics'!$Q$12+('Metrics'!$B$12-'Metrics'!$I$12)/('Metrics'!$J$12-'Metrics'!$I$12)*('Metrics'!$R$12-'Metrics'!$Q$12)),IF('Metrics'!$B$12&lt;='Metrics'!$K$12,IF('Metrics'!$K$12-'Metrics'!$J$12&lt;=0,'Metrics'!$S$12,'Metrics'!$R$12+('Metrics'!$B$12-'Metrics'!$J$12)/('Metrics'!$K$12-'Metrics'!$J$12)*('Metrics'!$S$12-'Metrics'!$R$12)),IF('Metrics'!$B$12&lt;='Metrics'!$L$12,IF('Metrics'!$L$12-'Metrics'!$K$12&lt;=0,'Metrics'!$T$12,'Metrics'!$S$12+('Metrics'!$B$12-'Metrics'!$K$12)/('Metrics'!$L$12-'Metrics'!$K$12)*('Metrics'!$T$12-'Metrics'!$S$12)),IF('Metrics'!$M$12-'Metrics'!$L$12&lt;=0,'Metrics'!$U$12,'Metrics'!$T$12+('Metrics'!$B$12-'Metrics'!$L$12)/('Metrics'!$M$12-'Metrics'!$L$12)*('Metrics'!$U$12-'Metrics'!$T$12)))))))))))),"")</f>
         <v/>
       </c>
@@ -4124,87 +4117,87 @@
           <t>Bankfull height above channel</t>
         </is>
       </c>
-      <c r="B13" s="76">
+      <c r="B13" s="75">
         <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
         <v/>
       </c>
-      <c r="C13" s="76">
+      <c r="C13" s="75">
         <f>IF('DEEP Score'!$F$23="","All streams (pooled)",'DEEP Score'!$F$23)</f>
         <v/>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="75">
         <f>"spring_phab_xbkf_h|"&amp;'Metrics'!$C$13</f>
         <v/>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$13,curve_key,0),MATCH("spring_phab_xbkf_h|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="I13" s="76">
+      <c r="I13" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="J13" s="76">
+      <c r="J13" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="K13" s="76">
+      <c r="K13" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="L13" s="76">
+      <c r="L13" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="M13" s="76">
+      <c r="M13" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="N13" s="76">
+      <c r="N13" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="O13" s="76">
+      <c r="O13" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="Q13" s="76">
+      <c r="Q13" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="R13" s="76">
+      <c r="R13" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="S13" s="76">
+      <c r="S13" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="T13" s="76">
+      <c r="T13" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="U13" s="76">
+      <c r="U13" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$13)</f>
         <v/>
       </c>
-      <c r="V13" s="77">
+      <c r="V13" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$13),MAX(0,MIN(1,IF('Metrics'!$B$13&lt;='Metrics'!$F$13,'Metrics'!$N$13,IF('Metrics'!$B$13&gt;='Metrics'!$M$13,'Metrics'!$U$13,IF('Metrics'!$B$13&lt;='Metrics'!$G$13,IF('Metrics'!$G$13-'Metrics'!$F$13&lt;=0,'Metrics'!$O$13,'Metrics'!$N$13+('Metrics'!$B$13-'Metrics'!$F$13)/('Metrics'!$G$13-'Metrics'!$F$13)*('Metrics'!$O$13-'Metrics'!$N$13)),IF('Metrics'!$B$13&lt;='Metrics'!$H$13,IF('Metrics'!$H$13-'Metrics'!$G$13&lt;=0,'Metrics'!$P$13,'Metrics'!$O$13+('Metrics'!$B$13-'Metrics'!$G$13)/('Metrics'!$H$13-'Metrics'!$G$13)*('Metrics'!$P$13-'Metrics'!$O$13)),IF('Metrics'!$B$13&lt;='Metrics'!$I$13,IF('Metrics'!$I$13-'Metrics'!$H$13&lt;=0,'Metrics'!$Q$13,'Metrics'!$P$13+('Metrics'!$B$13-'Metrics'!$H$13)/('Metrics'!$I$13-'Metrics'!$H$13)*('Metrics'!$Q$13-'Metrics'!$P$13)),IF('Metrics'!$B$13&lt;='Metrics'!$J$13,IF('Metrics'!$J$13-'Metrics'!$I$13&lt;=0,'Metrics'!$R$13,'Metrics'!$Q$13+('Metrics'!$B$13-'Metrics'!$I$13)/('Metrics'!$J$13-'Metrics'!$I$13)*('Metrics'!$R$13-'Metrics'!$Q$13)),IF('Metrics'!$B$13&lt;='Metrics'!$K$13,IF('Metrics'!$K$13-'Metrics'!$J$13&lt;=0,'Metrics'!$S$13,'Metrics'!$R$13+('Metrics'!$B$13-'Metrics'!$J$13)/('Metrics'!$K$13-'Metrics'!$J$13)*('Metrics'!$S$13-'Metrics'!$R$13)),IF('Metrics'!$B$13&lt;='Metrics'!$L$13,IF('Metrics'!$L$13-'Metrics'!$K$13&lt;=0,'Metrics'!$T$13,'Metrics'!$S$13+('Metrics'!$B$13-'Metrics'!$K$13)/('Metrics'!$L$13-'Metrics'!$K$13)*('Metrics'!$T$13-'Metrics'!$S$13)),IF('Metrics'!$M$13-'Metrics'!$L$13&lt;=0,'Metrics'!$U$13,'Metrics'!$T$13+('Metrics'!$B$13-'Metrics'!$L$13)/('Metrics'!$M$13-'Metrics'!$L$13)*('Metrics'!$U$13-'Metrics'!$T$13)))))))))))),"")</f>
         <v/>
       </c>
@@ -4215,87 +4208,87 @@
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="B14" s="76">
+      <c r="B14" s="75">
         <f>IF('DEEP Score'!$E$24="","",'DEEP Score'!$E$24)</f>
         <v/>
       </c>
-      <c r="C14" s="76">
+      <c r="C14" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="75">
         <f>"spring_phab_pct_safn|"&amp;'Metrics'!$C$14</f>
         <v/>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$14,curve_key,0),MATCH("spring_phab_pct_safn|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="I14" s="76">
+      <c r="I14" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="J14" s="76">
+      <c r="J14" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="K14" s="76">
+      <c r="K14" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="L14" s="76">
+      <c r="L14" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="M14" s="76">
+      <c r="M14" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="N14" s="76">
+      <c r="N14" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="O14" s="76">
+      <c r="O14" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="Q14" s="76">
+      <c r="Q14" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="R14" s="76">
+      <c r="R14" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="S14" s="76">
+      <c r="S14" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="T14" s="76">
+      <c r="T14" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="U14" s="76">
+      <c r="U14" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$14)</f>
         <v/>
       </c>
-      <c r="V14" s="77">
+      <c r="V14" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$14),MAX(0,MIN(1,IF('Metrics'!$B$14&lt;='Metrics'!$F$14,'Metrics'!$N$14,IF('Metrics'!$B$14&gt;='Metrics'!$M$14,'Metrics'!$U$14,IF('Metrics'!$B$14&lt;='Metrics'!$G$14,IF('Metrics'!$G$14-'Metrics'!$F$14&lt;=0,'Metrics'!$O$14,'Metrics'!$N$14+('Metrics'!$B$14-'Metrics'!$F$14)/('Metrics'!$G$14-'Metrics'!$F$14)*('Metrics'!$O$14-'Metrics'!$N$14)),IF('Metrics'!$B$14&lt;='Metrics'!$H$14,IF('Metrics'!$H$14-'Metrics'!$G$14&lt;=0,'Metrics'!$P$14,'Metrics'!$O$14+('Metrics'!$B$14-'Metrics'!$G$14)/('Metrics'!$H$14-'Metrics'!$G$14)*('Metrics'!$P$14-'Metrics'!$O$14)),IF('Metrics'!$B$14&lt;='Metrics'!$I$14,IF('Metrics'!$I$14-'Metrics'!$H$14&lt;=0,'Metrics'!$Q$14,'Metrics'!$P$14+('Metrics'!$B$14-'Metrics'!$H$14)/('Metrics'!$I$14-'Metrics'!$H$14)*('Metrics'!$Q$14-'Metrics'!$P$14)),IF('Metrics'!$B$14&lt;='Metrics'!$J$14,IF('Metrics'!$J$14-'Metrics'!$I$14&lt;=0,'Metrics'!$R$14,'Metrics'!$Q$14+('Metrics'!$B$14-'Metrics'!$I$14)/('Metrics'!$J$14-'Metrics'!$I$14)*('Metrics'!$R$14-'Metrics'!$Q$14)),IF('Metrics'!$B$14&lt;='Metrics'!$K$14,IF('Metrics'!$K$14-'Metrics'!$J$14&lt;=0,'Metrics'!$S$14,'Metrics'!$R$14+('Metrics'!$B$14-'Metrics'!$J$14)/('Metrics'!$K$14-'Metrics'!$J$14)*('Metrics'!$S$14-'Metrics'!$R$14)),IF('Metrics'!$B$14&lt;='Metrics'!$L$14,IF('Metrics'!$L$14-'Metrics'!$K$14&lt;=0,'Metrics'!$T$14,'Metrics'!$S$14+('Metrics'!$B$14-'Metrics'!$K$14)/('Metrics'!$L$14-'Metrics'!$K$14)*('Metrics'!$T$14-'Metrics'!$S$14)),IF('Metrics'!$M$14-'Metrics'!$L$14&lt;=0,'Metrics'!$U$14,'Metrics'!$T$14+('Metrics'!$B$14-'Metrics'!$L$14)/('Metrics'!$M$14-'Metrics'!$L$14)*('Metrics'!$U$14-'Metrics'!$T$14)))))))))))),"")</f>
         <v/>
       </c>
@@ -4306,87 +4299,87 @@
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="B15" s="76">
+      <c r="B15" s="75">
         <f>IF('DEEP Score'!$E$25="","",'DEEP Score'!$E$25)</f>
         <v/>
       </c>
-      <c r="C15" s="76">
+      <c r="C15" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="75">
         <f>"spring_phab_xembed|"&amp;'Metrics'!$C$15</f>
         <v/>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$15,curve_key,0),MATCH("spring_phab_xembed|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="K15" s="76">
+      <c r="K15" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="L15" s="76">
+      <c r="L15" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="M15" s="76">
+      <c r="M15" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="N15" s="76">
+      <c r="N15" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="O15" s="76">
+      <c r="O15" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="P15" s="76">
+      <c r="P15" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="Q15" s="76">
+      <c r="Q15" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="R15" s="76">
+      <c r="R15" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="S15" s="76">
+      <c r="S15" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="T15" s="76">
+      <c r="T15" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="U15" s="76">
+      <c r="U15" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$15)</f>
         <v/>
       </c>
-      <c r="V15" s="77">
+      <c r="V15" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$15),MAX(0,MIN(1,IF('Metrics'!$B$15&lt;='Metrics'!$F$15,'Metrics'!$N$15,IF('Metrics'!$B$15&gt;='Metrics'!$M$15,'Metrics'!$U$15,IF('Metrics'!$B$15&lt;='Metrics'!$G$15,IF('Metrics'!$G$15-'Metrics'!$F$15&lt;=0,'Metrics'!$O$15,'Metrics'!$N$15+('Metrics'!$B$15-'Metrics'!$F$15)/('Metrics'!$G$15-'Metrics'!$F$15)*('Metrics'!$O$15-'Metrics'!$N$15)),IF('Metrics'!$B$15&lt;='Metrics'!$H$15,IF('Metrics'!$H$15-'Metrics'!$G$15&lt;=0,'Metrics'!$P$15,'Metrics'!$O$15+('Metrics'!$B$15-'Metrics'!$G$15)/('Metrics'!$H$15-'Metrics'!$G$15)*('Metrics'!$P$15-'Metrics'!$O$15)),IF('Metrics'!$B$15&lt;='Metrics'!$I$15,IF('Metrics'!$I$15-'Metrics'!$H$15&lt;=0,'Metrics'!$Q$15,'Metrics'!$P$15+('Metrics'!$B$15-'Metrics'!$H$15)/('Metrics'!$I$15-'Metrics'!$H$15)*('Metrics'!$Q$15-'Metrics'!$P$15)),IF('Metrics'!$B$15&lt;='Metrics'!$J$15,IF('Metrics'!$J$15-'Metrics'!$I$15&lt;=0,'Metrics'!$R$15,'Metrics'!$Q$15+('Metrics'!$B$15-'Metrics'!$I$15)/('Metrics'!$J$15-'Metrics'!$I$15)*('Metrics'!$R$15-'Metrics'!$Q$15)),IF('Metrics'!$B$15&lt;='Metrics'!$K$15,IF('Metrics'!$K$15-'Metrics'!$J$15&lt;=0,'Metrics'!$S$15,'Metrics'!$R$15+('Metrics'!$B$15-'Metrics'!$J$15)/('Metrics'!$K$15-'Metrics'!$J$15)*('Metrics'!$S$15-'Metrics'!$R$15)),IF('Metrics'!$B$15&lt;='Metrics'!$L$15,IF('Metrics'!$L$15-'Metrics'!$K$15&lt;=0,'Metrics'!$T$15,'Metrics'!$S$15+('Metrics'!$B$15-'Metrics'!$K$15)/('Metrics'!$L$15-'Metrics'!$K$15)*('Metrics'!$T$15-'Metrics'!$S$15)),IF('Metrics'!$M$15-'Metrics'!$L$15&lt;=0,'Metrics'!$U$15,'Metrics'!$T$15+('Metrics'!$B$15-'Metrics'!$L$15)/('Metrics'!$M$15-'Metrics'!$L$15)*('Metrics'!$U$15-'Metrics'!$T$15)))))))))))),"")</f>
         <v/>
       </c>
@@ -4397,87 +4390,87 @@
           <t>Sinuosity</t>
         </is>
       </c>
-      <c r="B16" s="76">
+      <c r="B16" s="75">
         <f>IF('DEEP Score'!$E$28="","",'DEEP Score'!$E$28)</f>
         <v/>
       </c>
-      <c r="C16" s="76">
+      <c r="C16" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="75">
         <f>"spring_phab_sinu|"&amp;'Metrics'!$C$16</f>
         <v/>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$16,curve_key,0),MATCH("spring_phab_sinu|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F16" s="76">
+      <c r="F16" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="I16" s="76">
+      <c r="I16" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="J16" s="76">
+      <c r="J16" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="K16" s="76">
+      <c r="K16" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="L16" s="76">
+      <c r="L16" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="M16" s="76">
+      <c r="M16" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="N16" s="76">
+      <c r="N16" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="O16" s="76">
+      <c r="O16" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="P16" s="76">
+      <c r="P16" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="Q16" s="76">
+      <c r="Q16" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="R16" s="76">
+      <c r="R16" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="S16" s="76">
+      <c r="S16" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="T16" s="76">
+      <c r="T16" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="U16" s="76">
+      <c r="U16" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$16)</f>
         <v/>
       </c>
-      <c r="V16" s="77">
+      <c r="V16" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$16),MAX(0,MIN(1,IF('Metrics'!$B$16&lt;='Metrics'!$F$16,'Metrics'!$N$16,IF('Metrics'!$B$16&gt;='Metrics'!$M$16,'Metrics'!$U$16,IF('Metrics'!$B$16&lt;='Metrics'!$G$16,IF('Metrics'!$G$16-'Metrics'!$F$16&lt;=0,'Metrics'!$O$16,'Metrics'!$N$16+('Metrics'!$B$16-'Metrics'!$F$16)/('Metrics'!$G$16-'Metrics'!$F$16)*('Metrics'!$O$16-'Metrics'!$N$16)),IF('Metrics'!$B$16&lt;='Metrics'!$H$16,IF('Metrics'!$H$16-'Metrics'!$G$16&lt;=0,'Metrics'!$P$16,'Metrics'!$O$16+('Metrics'!$B$16-'Metrics'!$G$16)/('Metrics'!$H$16-'Metrics'!$G$16)*('Metrics'!$P$16-'Metrics'!$O$16)),IF('Metrics'!$B$16&lt;='Metrics'!$I$16,IF('Metrics'!$I$16-'Metrics'!$H$16&lt;=0,'Metrics'!$Q$16,'Metrics'!$P$16+('Metrics'!$B$16-'Metrics'!$H$16)/('Metrics'!$I$16-'Metrics'!$H$16)*('Metrics'!$Q$16-'Metrics'!$P$16)),IF('Metrics'!$B$16&lt;='Metrics'!$J$16,IF('Metrics'!$J$16-'Metrics'!$I$16&lt;=0,'Metrics'!$R$16,'Metrics'!$Q$16+('Metrics'!$B$16-'Metrics'!$I$16)/('Metrics'!$J$16-'Metrics'!$I$16)*('Metrics'!$R$16-'Metrics'!$Q$16)),IF('Metrics'!$B$16&lt;='Metrics'!$K$16,IF('Metrics'!$K$16-'Metrics'!$J$16&lt;=0,'Metrics'!$S$16,'Metrics'!$R$16+('Metrics'!$B$16-'Metrics'!$J$16)/('Metrics'!$K$16-'Metrics'!$J$16)*('Metrics'!$S$16-'Metrics'!$R$16)),IF('Metrics'!$B$16&lt;='Metrics'!$L$16,IF('Metrics'!$L$16-'Metrics'!$K$16&lt;=0,'Metrics'!$T$16,'Metrics'!$S$16+('Metrics'!$B$16-'Metrics'!$K$16)/('Metrics'!$L$16-'Metrics'!$K$16)*('Metrics'!$T$16-'Metrics'!$S$16)),IF('Metrics'!$M$16-'Metrics'!$L$16&lt;=0,'Metrics'!$U$16,'Metrics'!$T$16+('Metrics'!$B$16-'Metrics'!$L$16)/('Metrics'!$M$16-'Metrics'!$L$16)*('Metrics'!$U$16-'Metrics'!$T$16)))))))))))),"")</f>
         <v/>
       </c>
@@ -4488,87 +4481,87 @@
           <t>Bank angle</t>
         </is>
       </c>
-      <c r="B17" s="76">
+      <c r="B17" s="75">
         <f>IF('DEEP Score'!$E$29="","",'DEEP Score'!$E$29)</f>
         <v/>
       </c>
-      <c r="C17" s="76">
+      <c r="C17" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D17" s="76">
+      <c r="D17" s="75">
         <f>"spring_phab_xbka|"&amp;'Metrics'!$C$17</f>
         <v/>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$17,curve_key,0),MATCH("spring_phab_xbka|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="H17" s="76">
+      <c r="H17" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="L17" s="76">
+      <c r="L17" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="M17" s="76">
+      <c r="M17" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="N17" s="76">
+      <c r="N17" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="O17" s="76">
+      <c r="O17" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="P17" s="76">
+      <c r="P17" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="Q17" s="76">
+      <c r="Q17" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="R17" s="76">
+      <c r="R17" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="S17" s="76">
+      <c r="S17" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="T17" s="76">
+      <c r="T17" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="U17" s="76">
+      <c r="U17" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$17)</f>
         <v/>
       </c>
-      <c r="V17" s="77">
+      <c r="V17" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$17),MAX(0,MIN(1,IF('Metrics'!$B$17&lt;='Metrics'!$F$17,'Metrics'!$N$17,IF('Metrics'!$B$17&gt;='Metrics'!$M$17,'Metrics'!$U$17,IF('Metrics'!$B$17&lt;='Metrics'!$G$17,IF('Metrics'!$G$17-'Metrics'!$F$17&lt;=0,'Metrics'!$O$17,'Metrics'!$N$17+('Metrics'!$B$17-'Metrics'!$F$17)/('Metrics'!$G$17-'Metrics'!$F$17)*('Metrics'!$O$17-'Metrics'!$N$17)),IF('Metrics'!$B$17&lt;='Metrics'!$H$17,IF('Metrics'!$H$17-'Metrics'!$G$17&lt;=0,'Metrics'!$P$17,'Metrics'!$O$17+('Metrics'!$B$17-'Metrics'!$G$17)/('Metrics'!$H$17-'Metrics'!$G$17)*('Metrics'!$P$17-'Metrics'!$O$17)),IF('Metrics'!$B$17&lt;='Metrics'!$I$17,IF('Metrics'!$I$17-'Metrics'!$H$17&lt;=0,'Metrics'!$Q$17,'Metrics'!$P$17+('Metrics'!$B$17-'Metrics'!$H$17)/('Metrics'!$I$17-'Metrics'!$H$17)*('Metrics'!$Q$17-'Metrics'!$P$17)),IF('Metrics'!$B$17&lt;='Metrics'!$J$17,IF('Metrics'!$J$17-'Metrics'!$I$17&lt;=0,'Metrics'!$R$17,'Metrics'!$Q$17+('Metrics'!$B$17-'Metrics'!$I$17)/('Metrics'!$J$17-'Metrics'!$I$17)*('Metrics'!$R$17-'Metrics'!$Q$17)),IF('Metrics'!$B$17&lt;='Metrics'!$K$17,IF('Metrics'!$K$17-'Metrics'!$J$17&lt;=0,'Metrics'!$S$17,'Metrics'!$R$17+('Metrics'!$B$17-'Metrics'!$J$17)/('Metrics'!$K$17-'Metrics'!$J$17)*('Metrics'!$S$17-'Metrics'!$R$17)),IF('Metrics'!$B$17&lt;='Metrics'!$L$17,IF('Metrics'!$L$17-'Metrics'!$K$17&lt;=0,'Metrics'!$T$17,'Metrics'!$S$17+('Metrics'!$B$17-'Metrics'!$K$17)/('Metrics'!$L$17-'Metrics'!$K$17)*('Metrics'!$T$17-'Metrics'!$S$17)),IF('Metrics'!$M$17-'Metrics'!$L$17&lt;=0,'Metrics'!$U$17,'Metrics'!$T$17+('Metrics'!$B$17-'Metrics'!$L$17)/('Metrics'!$M$17-'Metrics'!$L$17)*('Metrics'!$U$17-'Metrics'!$T$17)))))))))))),"")</f>
         <v/>
       </c>
@@ -4579,87 +4572,87 @@
           <t>Relative bed stability</t>
         </is>
       </c>
-      <c r="B18" s="76">
+      <c r="B18" s="75">
         <f>IF('DEEP Score'!$E$30="","",'DEEP Score'!$E$30)</f>
         <v/>
       </c>
-      <c r="C18" s="76">
+      <c r="C18" s="75">
         <f>IF('DEEP Score'!$F$30="","All streams (pooled)",'DEEP Score'!$F$30)</f>
         <v/>
       </c>
-      <c r="D18" s="76">
+      <c r="D18" s="75">
         <f>"spring_phab_lrbs_use|"&amp;'Metrics'!$C$18</f>
         <v/>
       </c>
-      <c r="E18" s="76">
+      <c r="E18" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$18,curve_key,0),MATCH("spring_phab_lrbs_use|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="I18" s="76">
+      <c r="I18" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="J18" s="76">
+      <c r="J18" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="L18" s="76">
+      <c r="L18" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="M18" s="76">
+      <c r="M18" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="N18" s="76">
+      <c r="N18" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="O18" s="76">
+      <c r="O18" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="P18" s="76">
+      <c r="P18" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="Q18" s="76">
+      <c r="Q18" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="R18" s="76">
+      <c r="R18" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="S18" s="76">
+      <c r="S18" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="T18" s="76">
+      <c r="T18" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="U18" s="76">
+      <c r="U18" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$18)</f>
         <v/>
       </c>
-      <c r="V18" s="77">
+      <c r="V18" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$18),MAX(0,MIN(1,IF('Metrics'!$B$18&lt;='Metrics'!$F$18,'Metrics'!$N$18,IF('Metrics'!$B$18&gt;='Metrics'!$M$18,'Metrics'!$U$18,IF('Metrics'!$B$18&lt;='Metrics'!$G$18,IF('Metrics'!$G$18-'Metrics'!$F$18&lt;=0,'Metrics'!$O$18,'Metrics'!$N$18+('Metrics'!$B$18-'Metrics'!$F$18)/('Metrics'!$G$18-'Metrics'!$F$18)*('Metrics'!$O$18-'Metrics'!$N$18)),IF('Metrics'!$B$18&lt;='Metrics'!$H$18,IF('Metrics'!$H$18-'Metrics'!$G$18&lt;=0,'Metrics'!$P$18,'Metrics'!$O$18+('Metrics'!$B$18-'Metrics'!$G$18)/('Metrics'!$H$18-'Metrics'!$G$18)*('Metrics'!$P$18-'Metrics'!$O$18)),IF('Metrics'!$B$18&lt;='Metrics'!$I$18,IF('Metrics'!$I$18-'Metrics'!$H$18&lt;=0,'Metrics'!$Q$18,'Metrics'!$P$18+('Metrics'!$B$18-'Metrics'!$H$18)/('Metrics'!$I$18-'Metrics'!$H$18)*('Metrics'!$Q$18-'Metrics'!$P$18)),IF('Metrics'!$B$18&lt;='Metrics'!$J$18,IF('Metrics'!$J$18-'Metrics'!$I$18&lt;=0,'Metrics'!$R$18,'Metrics'!$Q$18+('Metrics'!$B$18-'Metrics'!$I$18)/('Metrics'!$J$18-'Metrics'!$I$18)*('Metrics'!$R$18-'Metrics'!$Q$18)),IF('Metrics'!$B$18&lt;='Metrics'!$K$18,IF('Metrics'!$K$18-'Metrics'!$J$18&lt;=0,'Metrics'!$S$18,'Metrics'!$R$18+('Metrics'!$B$18-'Metrics'!$J$18)/('Metrics'!$K$18-'Metrics'!$J$18)*('Metrics'!$S$18-'Metrics'!$R$18)),IF('Metrics'!$B$18&lt;='Metrics'!$L$18,IF('Metrics'!$L$18-'Metrics'!$K$18&lt;=0,'Metrics'!$T$18,'Metrics'!$S$18+('Metrics'!$B$18-'Metrics'!$K$18)/('Metrics'!$L$18-'Metrics'!$K$18)*('Metrics'!$T$18-'Metrics'!$S$18)),IF('Metrics'!$M$18-'Metrics'!$L$18&lt;=0,'Metrics'!$U$18,'Metrics'!$T$18+('Metrics'!$B$18-'Metrics'!$L$18)/('Metrics'!$M$18-'Metrics'!$L$18)*('Metrics'!$U$18-'Metrics'!$T$18)))))))))))),"")</f>
         <v/>
       </c>
@@ -4667,90 +4660,90 @@
     <row r="19">
       <c r="A19" s="41" t="inlineStr">
         <is>
-          <t>Substrate size</t>
-        </is>
-      </c>
-      <c r="B19" s="76">
+          <t>Large wood volume</t>
+        </is>
+      </c>
+      <c r="B19" s="75">
         <f>IF('DEEP Score'!$E$32="","",'DEEP Score'!$E$32)</f>
         <v/>
       </c>
-      <c r="C19" s="76">
+      <c r="C19" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D19" s="76">
-        <f>"spring_phab_lsub_dmm|"&amp;'Metrics'!$C$19</f>
-        <v/>
-      </c>
-      <c r="E19" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_lsub_dmm|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F19" s="76">
+      <c r="D19" s="75">
+        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$19</f>
+        <v/>
+      </c>
+      <c r="E19" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F19" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="J19" s="76">
+      <c r="J19" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="L19" s="76">
+      <c r="L19" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="M19" s="76">
+      <c r="M19" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="N19" s="76">
+      <c r="N19" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="O19" s="76">
+      <c r="O19" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="P19" s="76">
+      <c r="P19" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="Q19" s="76">
+      <c r="Q19" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="R19" s="76">
+      <c r="R19" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="S19" s="76">
+      <c r="S19" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="T19" s="76">
+      <c r="T19" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="U19" s="76">
+      <c r="U19" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$19)</f>
         <v/>
       </c>
-      <c r="V19" s="77">
+      <c r="V19" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$19),MAX(0,MIN(1,IF('Metrics'!$B$19&lt;='Metrics'!$F$19,'Metrics'!$N$19,IF('Metrics'!$B$19&gt;='Metrics'!$M$19,'Metrics'!$U$19,IF('Metrics'!$B$19&lt;='Metrics'!$G$19,IF('Metrics'!$G$19-'Metrics'!$F$19&lt;=0,'Metrics'!$O$19,'Metrics'!$N$19+('Metrics'!$B$19-'Metrics'!$F$19)/('Metrics'!$G$19-'Metrics'!$F$19)*('Metrics'!$O$19-'Metrics'!$N$19)),IF('Metrics'!$B$19&lt;='Metrics'!$H$19,IF('Metrics'!$H$19-'Metrics'!$G$19&lt;=0,'Metrics'!$P$19,'Metrics'!$O$19+('Metrics'!$B$19-'Metrics'!$G$19)/('Metrics'!$H$19-'Metrics'!$G$19)*('Metrics'!$P$19-'Metrics'!$O$19)),IF('Metrics'!$B$19&lt;='Metrics'!$I$19,IF('Metrics'!$I$19-'Metrics'!$H$19&lt;=0,'Metrics'!$Q$19,'Metrics'!$P$19+('Metrics'!$B$19-'Metrics'!$H$19)/('Metrics'!$I$19-'Metrics'!$H$19)*('Metrics'!$Q$19-'Metrics'!$P$19)),IF('Metrics'!$B$19&lt;='Metrics'!$J$19,IF('Metrics'!$J$19-'Metrics'!$I$19&lt;=0,'Metrics'!$R$19,'Metrics'!$Q$19+('Metrics'!$B$19-'Metrics'!$I$19)/('Metrics'!$J$19-'Metrics'!$I$19)*('Metrics'!$R$19-'Metrics'!$Q$19)),IF('Metrics'!$B$19&lt;='Metrics'!$K$19,IF('Metrics'!$K$19-'Metrics'!$J$19&lt;=0,'Metrics'!$S$19,'Metrics'!$R$19+('Metrics'!$B$19-'Metrics'!$J$19)/('Metrics'!$K$19-'Metrics'!$J$19)*('Metrics'!$S$19-'Metrics'!$R$19)),IF('Metrics'!$B$19&lt;='Metrics'!$L$19,IF('Metrics'!$L$19-'Metrics'!$K$19&lt;=0,'Metrics'!$T$19,'Metrics'!$S$19+('Metrics'!$B$19-'Metrics'!$K$19)/('Metrics'!$L$19-'Metrics'!$K$19)*('Metrics'!$T$19-'Metrics'!$S$19)),IF('Metrics'!$M$19-'Metrics'!$L$19&lt;=0,'Metrics'!$U$19,'Metrics'!$T$19+('Metrics'!$B$19-'Metrics'!$L$19)/('Metrics'!$M$19-'Metrics'!$L$19)*('Metrics'!$U$19-'Metrics'!$T$19)))))))))))),"")</f>
         <v/>
       </c>
@@ -4758,90 +4751,90 @@
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
-        </is>
-      </c>
-      <c r="B20" s="76">
+          <t>Substrate size</t>
+        </is>
+      </c>
+      <c r="B20" s="75">
         <f>IF('DEEP Score'!$E$33="","",'DEEP Score'!$E$33)</f>
         <v/>
       </c>
-      <c r="C20" s="76">
+      <c r="C20" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D20" s="76">
-        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$20</f>
-        <v/>
-      </c>
-      <c r="E20" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F20" s="76">
+      <c r="D20" s="75">
+        <f>"spring_phab_lsub_dmm|"&amp;'Metrics'!$C$20</f>
+        <v/>
+      </c>
+      <c r="E20" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_phab_lsub_dmm|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F20" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="J20" s="76">
+      <c r="J20" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="L20" s="76">
+      <c r="L20" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="M20" s="76">
+      <c r="M20" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="N20" s="76">
+      <c r="N20" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="O20" s="76">
+      <c r="O20" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="P20" s="76">
+      <c r="P20" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="Q20" s="76">
+      <c r="Q20" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="R20" s="76">
+      <c r="R20" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="S20" s="76">
+      <c r="S20" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="T20" s="76">
+      <c r="T20" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="U20" s="76">
+      <c r="U20" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$20)</f>
         <v/>
       </c>
-      <c r="V20" s="77">
+      <c r="V20" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$20),MAX(0,MIN(1,IF('Metrics'!$B$20&lt;='Metrics'!$F$20,'Metrics'!$N$20,IF('Metrics'!$B$20&gt;='Metrics'!$M$20,'Metrics'!$U$20,IF('Metrics'!$B$20&lt;='Metrics'!$G$20,IF('Metrics'!$G$20-'Metrics'!$F$20&lt;=0,'Metrics'!$O$20,'Metrics'!$N$20+('Metrics'!$B$20-'Metrics'!$F$20)/('Metrics'!$G$20-'Metrics'!$F$20)*('Metrics'!$O$20-'Metrics'!$N$20)),IF('Metrics'!$B$20&lt;='Metrics'!$H$20,IF('Metrics'!$H$20-'Metrics'!$G$20&lt;=0,'Metrics'!$P$20,'Metrics'!$O$20+('Metrics'!$B$20-'Metrics'!$G$20)/('Metrics'!$H$20-'Metrics'!$G$20)*('Metrics'!$P$20-'Metrics'!$O$20)),IF('Metrics'!$B$20&lt;='Metrics'!$I$20,IF('Metrics'!$I$20-'Metrics'!$H$20&lt;=0,'Metrics'!$Q$20,'Metrics'!$P$20+('Metrics'!$B$20-'Metrics'!$H$20)/('Metrics'!$I$20-'Metrics'!$H$20)*('Metrics'!$Q$20-'Metrics'!$P$20)),IF('Metrics'!$B$20&lt;='Metrics'!$J$20,IF('Metrics'!$J$20-'Metrics'!$I$20&lt;=0,'Metrics'!$R$20,'Metrics'!$Q$20+('Metrics'!$B$20-'Metrics'!$I$20)/('Metrics'!$J$20-'Metrics'!$I$20)*('Metrics'!$R$20-'Metrics'!$Q$20)),IF('Metrics'!$B$20&lt;='Metrics'!$K$20,IF('Metrics'!$K$20-'Metrics'!$J$20&lt;=0,'Metrics'!$S$20,'Metrics'!$R$20+('Metrics'!$B$20-'Metrics'!$J$20)/('Metrics'!$K$20-'Metrics'!$J$20)*('Metrics'!$S$20-'Metrics'!$R$20)),IF('Metrics'!$B$20&lt;='Metrics'!$L$20,IF('Metrics'!$L$20-'Metrics'!$K$20&lt;=0,'Metrics'!$T$20,'Metrics'!$S$20+('Metrics'!$B$20-'Metrics'!$K$20)/('Metrics'!$L$20-'Metrics'!$K$20)*('Metrics'!$T$20-'Metrics'!$S$20)),IF('Metrics'!$M$20-'Metrics'!$L$20&lt;=0,'Metrics'!$U$20,'Metrics'!$T$20+('Metrics'!$B$20-'Metrics'!$L$20)/('Metrics'!$M$20-'Metrics'!$L$20)*('Metrics'!$U$20-'Metrics'!$T$20)))))))))))),"")</f>
         <v/>
       </c>
@@ -4852,87 +4845,87 @@
           <t>Chlorophyll a</t>
         </is>
       </c>
-      <c r="B21" s="76">
+      <c r="B21" s="75">
         <f>IF('DEEP Score'!$E$35="","",'DEEP Score'!$E$35)</f>
         <v/>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D21" s="76">
+      <c r="D21" s="75">
         <f>"spring_chem_chla|"&amp;'Metrics'!$C$21</f>
         <v/>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_chem_chla|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F21" s="76">
+      <c r="F21" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="H21" s="76">
+      <c r="H21" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="I21" s="76">
+      <c r="I21" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="J21" s="76">
+      <c r="J21" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="K21" s="76">
+      <c r="K21" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="L21" s="76">
+      <c r="L21" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="M21" s="76">
+      <c r="M21" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="N21" s="76">
+      <c r="N21" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="O21" s="76">
+      <c r="O21" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="P21" s="76">
+      <c r="P21" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="Q21" s="76">
+      <c r="Q21" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="R21" s="76">
+      <c r="R21" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="S21" s="76">
+      <c r="S21" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="T21" s="76">
+      <c r="T21" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="U21" s="76">
+      <c r="U21" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$21)</f>
         <v/>
       </c>
-      <c r="V21" s="77">
+      <c r="V21" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$21),MAX(0,MIN(1,IF('Metrics'!$B$21&lt;='Metrics'!$F$21,'Metrics'!$N$21,IF('Metrics'!$B$21&gt;='Metrics'!$M$21,'Metrics'!$U$21,IF('Metrics'!$B$21&lt;='Metrics'!$G$21,IF('Metrics'!$G$21-'Metrics'!$F$21&lt;=0,'Metrics'!$O$21,'Metrics'!$N$21+('Metrics'!$B$21-'Metrics'!$F$21)/('Metrics'!$G$21-'Metrics'!$F$21)*('Metrics'!$O$21-'Metrics'!$N$21)),IF('Metrics'!$B$21&lt;='Metrics'!$H$21,IF('Metrics'!$H$21-'Metrics'!$G$21&lt;=0,'Metrics'!$P$21,'Metrics'!$O$21+('Metrics'!$B$21-'Metrics'!$G$21)/('Metrics'!$H$21-'Metrics'!$G$21)*('Metrics'!$P$21-'Metrics'!$O$21)),IF('Metrics'!$B$21&lt;='Metrics'!$I$21,IF('Metrics'!$I$21-'Metrics'!$H$21&lt;=0,'Metrics'!$Q$21,'Metrics'!$P$21+('Metrics'!$B$21-'Metrics'!$H$21)/('Metrics'!$I$21-'Metrics'!$H$21)*('Metrics'!$Q$21-'Metrics'!$P$21)),IF('Metrics'!$B$21&lt;='Metrics'!$J$21,IF('Metrics'!$J$21-'Metrics'!$I$21&lt;=0,'Metrics'!$R$21,'Metrics'!$Q$21+('Metrics'!$B$21-'Metrics'!$I$21)/('Metrics'!$J$21-'Metrics'!$I$21)*('Metrics'!$R$21-'Metrics'!$Q$21)),IF('Metrics'!$B$21&lt;='Metrics'!$K$21,IF('Metrics'!$K$21-'Metrics'!$J$21&lt;=0,'Metrics'!$S$21,'Metrics'!$R$21+('Metrics'!$B$21-'Metrics'!$J$21)/('Metrics'!$K$21-'Metrics'!$J$21)*('Metrics'!$S$21-'Metrics'!$R$21)),IF('Metrics'!$B$21&lt;='Metrics'!$L$21,IF('Metrics'!$L$21-'Metrics'!$K$21&lt;=0,'Metrics'!$T$21,'Metrics'!$S$21+('Metrics'!$B$21-'Metrics'!$K$21)/('Metrics'!$L$21-'Metrics'!$K$21)*('Metrics'!$T$21-'Metrics'!$S$21)),IF('Metrics'!$M$21-'Metrics'!$L$21&lt;=0,'Metrics'!$U$21,'Metrics'!$T$21+('Metrics'!$B$21-'Metrics'!$L$21)/('Metrics'!$M$21-'Metrics'!$L$21)*('Metrics'!$U$21-'Metrics'!$T$21)))))))))))),"")</f>
         <v/>
       </c>
@@ -4943,87 +4936,87 @@
           <t>Canopy density, mid-channel</t>
         </is>
       </c>
-      <c r="B22" s="76">
+      <c r="B22" s="75">
         <f>IF('DEEP Score'!$E$36="","",'DEEP Score'!$E$36)</f>
         <v/>
       </c>
-      <c r="C22" s="76">
+      <c r="C22" s="75">
         <f>IF('DEEP Score'!$F$36="","All streams (pooled)",'DEEP Score'!$F$36)</f>
         <v/>
       </c>
-      <c r="D22" s="76">
+      <c r="D22" s="75">
         <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$22</f>
         <v/>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_phab_xcdenmid|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F22" s="76">
+      <c r="F22" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="G22" s="76">
+      <c r="G22" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="H22" s="76">
+      <c r="H22" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="I22" s="76">
+      <c r="I22" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="J22" s="76">
+      <c r="J22" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="K22" s="76">
+      <c r="K22" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="L22" s="76">
+      <c r="L22" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="M22" s="76">
+      <c r="M22" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="N22" s="76">
+      <c r="N22" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="O22" s="76">
+      <c r="O22" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="P22" s="76">
+      <c r="P22" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="Q22" s="76">
+      <c r="Q22" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="R22" s="76">
+      <c r="R22" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="S22" s="76">
+      <c r="S22" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="T22" s="76">
+      <c r="T22" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="U22" s="76">
+      <c r="U22" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$22)</f>
         <v/>
       </c>
-      <c r="V22" s="77">
+      <c r="V22" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$22),MAX(0,MIN(1,IF('Metrics'!$B$22&lt;='Metrics'!$F$22,'Metrics'!$N$22,IF('Metrics'!$B$22&gt;='Metrics'!$M$22,'Metrics'!$U$22,IF('Metrics'!$B$22&lt;='Metrics'!$G$22,IF('Metrics'!$G$22-'Metrics'!$F$22&lt;=0,'Metrics'!$O$22,'Metrics'!$N$22+('Metrics'!$B$22-'Metrics'!$F$22)/('Metrics'!$G$22-'Metrics'!$F$22)*('Metrics'!$O$22-'Metrics'!$N$22)),IF('Metrics'!$B$22&lt;='Metrics'!$H$22,IF('Metrics'!$H$22-'Metrics'!$G$22&lt;=0,'Metrics'!$P$22,'Metrics'!$O$22+('Metrics'!$B$22-'Metrics'!$G$22)/('Metrics'!$H$22-'Metrics'!$G$22)*('Metrics'!$P$22-'Metrics'!$O$22)),IF('Metrics'!$B$22&lt;='Metrics'!$I$22,IF('Metrics'!$I$22-'Metrics'!$H$22&lt;=0,'Metrics'!$Q$22,'Metrics'!$P$22+('Metrics'!$B$22-'Metrics'!$H$22)/('Metrics'!$I$22-'Metrics'!$H$22)*('Metrics'!$Q$22-'Metrics'!$P$22)),IF('Metrics'!$B$22&lt;='Metrics'!$J$22,IF('Metrics'!$J$22-'Metrics'!$I$22&lt;=0,'Metrics'!$R$22,'Metrics'!$Q$22+('Metrics'!$B$22-'Metrics'!$I$22)/('Metrics'!$J$22-'Metrics'!$I$22)*('Metrics'!$R$22-'Metrics'!$Q$22)),IF('Metrics'!$B$22&lt;='Metrics'!$K$22,IF('Metrics'!$K$22-'Metrics'!$J$22&lt;=0,'Metrics'!$S$22,'Metrics'!$R$22+('Metrics'!$B$22-'Metrics'!$J$22)/('Metrics'!$K$22-'Metrics'!$J$22)*('Metrics'!$S$22-'Metrics'!$R$22)),IF('Metrics'!$B$22&lt;='Metrics'!$L$22,IF('Metrics'!$L$22-'Metrics'!$K$22&lt;=0,'Metrics'!$T$22,'Metrics'!$S$22+('Metrics'!$B$22-'Metrics'!$K$22)/('Metrics'!$L$22-'Metrics'!$K$22)*('Metrics'!$T$22-'Metrics'!$S$22)),IF('Metrics'!$M$22-'Metrics'!$L$22&lt;=0,'Metrics'!$U$22,'Metrics'!$T$22+('Metrics'!$B$22-'Metrics'!$L$22)/('Metrics'!$M$22-'Metrics'!$L$22)*('Metrics'!$U$22-'Metrics'!$T$22)))))))))))),"")</f>
         <v/>
       </c>
@@ -5034,87 +5027,87 @@
           <t>Riparian veg cover, woody</t>
         </is>
       </c>
-      <c r="B23" s="76">
+      <c r="B23" s="75">
         <f>IF('DEEP Score'!$E$37="","",'DEEP Score'!$E$37)</f>
         <v/>
       </c>
-      <c r="C23" s="76">
+      <c r="C23" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="75">
         <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$23</f>
         <v/>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="H23" s="76">
+      <c r="H23" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="I23" s="76">
+      <c r="I23" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="J23" s="76">
+      <c r="J23" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="K23" s="76">
+      <c r="K23" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="L23" s="76">
+      <c r="L23" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="M23" s="76">
+      <c r="M23" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="N23" s="76">
+      <c r="N23" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="O23" s="76">
+      <c r="O23" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="P23" s="76">
+      <c r="P23" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="Q23" s="76">
+      <c r="Q23" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="R23" s="76">
+      <c r="R23" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="S23" s="76">
+      <c r="S23" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="T23" s="76">
+      <c r="T23" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="U23" s="76">
+      <c r="U23" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$23)</f>
         <v/>
       </c>
-      <c r="V23" s="77">
+      <c r="V23" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$23),MAX(0,MIN(1,IF('Metrics'!$B$23&lt;='Metrics'!$F$23,'Metrics'!$N$23,IF('Metrics'!$B$23&gt;='Metrics'!$M$23,'Metrics'!$U$23,IF('Metrics'!$B$23&lt;='Metrics'!$G$23,IF('Metrics'!$G$23-'Metrics'!$F$23&lt;=0,'Metrics'!$O$23,'Metrics'!$N$23+('Metrics'!$B$23-'Metrics'!$F$23)/('Metrics'!$G$23-'Metrics'!$F$23)*('Metrics'!$O$23-'Metrics'!$N$23)),IF('Metrics'!$B$23&lt;='Metrics'!$H$23,IF('Metrics'!$H$23-'Metrics'!$G$23&lt;=0,'Metrics'!$P$23,'Metrics'!$O$23+('Metrics'!$B$23-'Metrics'!$G$23)/('Metrics'!$H$23-'Metrics'!$G$23)*('Metrics'!$P$23-'Metrics'!$O$23)),IF('Metrics'!$B$23&lt;='Metrics'!$I$23,IF('Metrics'!$I$23-'Metrics'!$H$23&lt;=0,'Metrics'!$Q$23,'Metrics'!$P$23+('Metrics'!$B$23-'Metrics'!$H$23)/('Metrics'!$I$23-'Metrics'!$H$23)*('Metrics'!$Q$23-'Metrics'!$P$23)),IF('Metrics'!$B$23&lt;='Metrics'!$J$23,IF('Metrics'!$J$23-'Metrics'!$I$23&lt;=0,'Metrics'!$R$23,'Metrics'!$Q$23+('Metrics'!$B$23-'Metrics'!$I$23)/('Metrics'!$J$23-'Metrics'!$I$23)*('Metrics'!$R$23-'Metrics'!$Q$23)),IF('Metrics'!$B$23&lt;='Metrics'!$K$23,IF('Metrics'!$K$23-'Metrics'!$J$23&lt;=0,'Metrics'!$S$23,'Metrics'!$R$23+('Metrics'!$B$23-'Metrics'!$J$23)/('Metrics'!$K$23-'Metrics'!$J$23)*('Metrics'!$S$23-'Metrics'!$R$23)),IF('Metrics'!$B$23&lt;='Metrics'!$L$23,IF('Metrics'!$L$23-'Metrics'!$K$23&lt;=0,'Metrics'!$T$23,'Metrics'!$S$23+('Metrics'!$B$23-'Metrics'!$K$23)/('Metrics'!$L$23-'Metrics'!$K$23)*('Metrics'!$T$23-'Metrics'!$S$23)),IF('Metrics'!$M$23-'Metrics'!$L$23&lt;=0,'Metrics'!$U$23,'Metrics'!$T$23+('Metrics'!$B$23-'Metrics'!$L$23)/('Metrics'!$M$23-'Metrics'!$L$23)*('Metrics'!$U$23-'Metrics'!$T$23)))))))))))),"")</f>
         <v/>
       </c>
@@ -5125,87 +5118,87 @@
           <t>Total nitrogen</t>
         </is>
       </c>
-      <c r="B24" s="76">
+      <c r="B24" s="75">
         <f>IF('DEEP Score'!$E$38="","",'DEEP Score'!$E$38)</f>
         <v/>
       </c>
-      <c r="C24" s="76">
+      <c r="C24" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="75">
         <f>"spring_chem_ntl|"&amp;'Metrics'!$C$24</f>
         <v/>
       </c>
-      <c r="E24" s="76">
+      <c r="E24" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F24" s="76">
+      <c r="F24" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="G24" s="76">
+      <c r="G24" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="H24" s="76">
+      <c r="H24" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="I24" s="76">
+      <c r="I24" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="J24" s="76">
+      <c r="J24" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="K24" s="76">
+      <c r="K24" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="L24" s="76">
+      <c r="L24" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="M24" s="76">
+      <c r="M24" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="N24" s="76">
+      <c r="N24" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="O24" s="76">
+      <c r="O24" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="P24" s="76">
+      <c r="P24" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="Q24" s="76">
+      <c r="Q24" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="R24" s="76">
+      <c r="R24" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="S24" s="76">
+      <c r="S24" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="T24" s="76">
+      <c r="T24" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="U24" s="76">
+      <c r="U24" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$24)</f>
         <v/>
       </c>
-      <c r="V24" s="77">
+      <c r="V24" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$24),MAX(0,MIN(1,IF('Metrics'!$B$24&lt;='Metrics'!$F$24,'Metrics'!$N$24,IF('Metrics'!$B$24&gt;='Metrics'!$M$24,'Metrics'!$U$24,IF('Metrics'!$B$24&lt;='Metrics'!$G$24,IF('Metrics'!$G$24-'Metrics'!$F$24&lt;=0,'Metrics'!$O$24,'Metrics'!$N$24+('Metrics'!$B$24-'Metrics'!$F$24)/('Metrics'!$G$24-'Metrics'!$F$24)*('Metrics'!$O$24-'Metrics'!$N$24)),IF('Metrics'!$B$24&lt;='Metrics'!$H$24,IF('Metrics'!$H$24-'Metrics'!$G$24&lt;=0,'Metrics'!$P$24,'Metrics'!$O$24+('Metrics'!$B$24-'Metrics'!$G$24)/('Metrics'!$H$24-'Metrics'!$G$24)*('Metrics'!$P$24-'Metrics'!$O$24)),IF('Metrics'!$B$24&lt;='Metrics'!$I$24,IF('Metrics'!$I$24-'Metrics'!$H$24&lt;=0,'Metrics'!$Q$24,'Metrics'!$P$24+('Metrics'!$B$24-'Metrics'!$H$24)/('Metrics'!$I$24-'Metrics'!$H$24)*('Metrics'!$Q$24-'Metrics'!$P$24)),IF('Metrics'!$B$24&lt;='Metrics'!$J$24,IF('Metrics'!$J$24-'Metrics'!$I$24&lt;=0,'Metrics'!$R$24,'Metrics'!$Q$24+('Metrics'!$B$24-'Metrics'!$I$24)/('Metrics'!$J$24-'Metrics'!$I$24)*('Metrics'!$R$24-'Metrics'!$Q$24)),IF('Metrics'!$B$24&lt;='Metrics'!$K$24,IF('Metrics'!$K$24-'Metrics'!$J$24&lt;=0,'Metrics'!$S$24,'Metrics'!$R$24+('Metrics'!$B$24-'Metrics'!$J$24)/('Metrics'!$K$24-'Metrics'!$J$24)*('Metrics'!$S$24-'Metrics'!$R$24)),IF('Metrics'!$B$24&lt;='Metrics'!$L$24,IF('Metrics'!$L$24-'Metrics'!$K$24&lt;=0,'Metrics'!$T$24,'Metrics'!$S$24+('Metrics'!$B$24-'Metrics'!$K$24)/('Metrics'!$L$24-'Metrics'!$K$24)*('Metrics'!$T$24-'Metrics'!$S$24)),IF('Metrics'!$M$24-'Metrics'!$L$24&lt;=0,'Metrics'!$U$24,'Metrics'!$T$24+('Metrics'!$B$24-'Metrics'!$L$24)/('Metrics'!$M$24-'Metrics'!$L$24)*('Metrics'!$U$24-'Metrics'!$T$24)))))))))))),"")</f>
         <v/>
       </c>
@@ -5216,87 +5209,87 @@
           <t>Total phosphorus</t>
         </is>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="75">
         <f>IF('DEEP Score'!$E$39="","",'DEEP Score'!$E$39)</f>
         <v/>
       </c>
-      <c r="C25" s="76">
+      <c r="C25" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D25" s="76">
+      <c r="D25" s="75">
         <f>"spring_chem_ptl|"&amp;'Metrics'!$C$25</f>
         <v/>
       </c>
-      <c r="E25" s="76">
+      <c r="E25" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F25" s="76">
+      <c r="F25" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="G25" s="76">
+      <c r="G25" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="H25" s="76">
+      <c r="H25" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="I25" s="76">
+      <c r="I25" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="J25" s="76">
+      <c r="J25" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="K25" s="76">
+      <c r="K25" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="L25" s="76">
+      <c r="L25" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="M25" s="76">
+      <c r="M25" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="N25" s="76">
+      <c r="N25" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="O25" s="76">
+      <c r="O25" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="P25" s="76">
+      <c r="P25" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="Q25" s="76">
+      <c r="Q25" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="R25" s="76">
+      <c r="R25" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="S25" s="76">
+      <c r="S25" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="T25" s="76">
+      <c r="T25" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="U25" s="76">
+      <c r="U25" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$25)</f>
         <v/>
       </c>
-      <c r="V25" s="77">
+      <c r="V25" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$25),MAX(0,MIN(1,IF('Metrics'!$B$25&lt;='Metrics'!$F$25,'Metrics'!$N$25,IF('Metrics'!$B$25&gt;='Metrics'!$M$25,'Metrics'!$U$25,IF('Metrics'!$B$25&lt;='Metrics'!$G$25,IF('Metrics'!$G$25-'Metrics'!$F$25&lt;=0,'Metrics'!$O$25,'Metrics'!$N$25+('Metrics'!$B$25-'Metrics'!$F$25)/('Metrics'!$G$25-'Metrics'!$F$25)*('Metrics'!$O$25-'Metrics'!$N$25)),IF('Metrics'!$B$25&lt;='Metrics'!$H$25,IF('Metrics'!$H$25-'Metrics'!$G$25&lt;=0,'Metrics'!$P$25,'Metrics'!$O$25+('Metrics'!$B$25-'Metrics'!$G$25)/('Metrics'!$H$25-'Metrics'!$G$25)*('Metrics'!$P$25-'Metrics'!$O$25)),IF('Metrics'!$B$25&lt;='Metrics'!$I$25,IF('Metrics'!$I$25-'Metrics'!$H$25&lt;=0,'Metrics'!$Q$25,'Metrics'!$P$25+('Metrics'!$B$25-'Metrics'!$H$25)/('Metrics'!$I$25-'Metrics'!$H$25)*('Metrics'!$Q$25-'Metrics'!$P$25)),IF('Metrics'!$B$25&lt;='Metrics'!$J$25,IF('Metrics'!$J$25-'Metrics'!$I$25&lt;=0,'Metrics'!$R$25,'Metrics'!$Q$25+('Metrics'!$B$25-'Metrics'!$I$25)/('Metrics'!$J$25-'Metrics'!$I$25)*('Metrics'!$R$25-'Metrics'!$Q$25)),IF('Metrics'!$B$25&lt;='Metrics'!$K$25,IF('Metrics'!$K$25-'Metrics'!$J$25&lt;=0,'Metrics'!$S$25,'Metrics'!$R$25+('Metrics'!$B$25-'Metrics'!$J$25)/('Metrics'!$K$25-'Metrics'!$J$25)*('Metrics'!$S$25-'Metrics'!$R$25)),IF('Metrics'!$B$25&lt;='Metrics'!$L$25,IF('Metrics'!$L$25-'Metrics'!$K$25&lt;=0,'Metrics'!$T$25,'Metrics'!$S$25+('Metrics'!$B$25-'Metrics'!$K$25)/('Metrics'!$L$25-'Metrics'!$K$25)*('Metrics'!$T$25-'Metrics'!$S$25)),IF('Metrics'!$M$25-'Metrics'!$L$25&lt;=0,'Metrics'!$U$25,'Metrics'!$T$25+('Metrics'!$B$25-'Metrics'!$L$25)/('Metrics'!$M$25-'Metrics'!$L$25)*('Metrics'!$U$25-'Metrics'!$T$25)))))))))))),"")</f>
         <v/>
       </c>
@@ -5307,87 +5300,87 @@
           <t>Specific conductivity</t>
         </is>
       </c>
-      <c r="B26" s="76">
+      <c r="B26" s="75">
         <f>IF('DEEP Score'!$E$40="","",'DEEP Score'!$E$40)</f>
         <v/>
       </c>
-      <c r="C26" s="76">
+      <c r="C26" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D26" s="76">
+      <c r="D26" s="75">
         <f>"spring_chem_cond|"&amp;'Metrics'!$C$26</f>
         <v/>
       </c>
-      <c r="E26" s="76">
+      <c r="E26" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_chem_cond|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F26" s="76">
+      <c r="F26" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="G26" s="76">
+      <c r="G26" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="H26" s="76">
+      <c r="H26" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="I26" s="76">
+      <c r="I26" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="J26" s="76">
+      <c r="J26" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="K26" s="76">
+      <c r="K26" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="L26" s="76">
+      <c r="L26" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="M26" s="76">
+      <c r="M26" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="N26" s="76">
+      <c r="N26" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="O26" s="76">
+      <c r="O26" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="P26" s="76">
+      <c r="P26" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="Q26" s="76">
+      <c r="Q26" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="R26" s="76">
+      <c r="R26" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="S26" s="76">
+      <c r="S26" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="T26" s="76">
+      <c r="T26" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="U26" s="76">
+      <c r="U26" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$26)</f>
         <v/>
       </c>
-      <c r="V26" s="77">
+      <c r="V26" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$26),MAX(0,MIN(1,IF('Metrics'!$B$26&lt;='Metrics'!$F$26,'Metrics'!$N$26,IF('Metrics'!$B$26&gt;='Metrics'!$M$26,'Metrics'!$U$26,IF('Metrics'!$B$26&lt;='Metrics'!$G$26,IF('Metrics'!$G$26-'Metrics'!$F$26&lt;=0,'Metrics'!$O$26,'Metrics'!$N$26+('Metrics'!$B$26-'Metrics'!$F$26)/('Metrics'!$G$26-'Metrics'!$F$26)*('Metrics'!$O$26-'Metrics'!$N$26)),IF('Metrics'!$B$26&lt;='Metrics'!$H$26,IF('Metrics'!$H$26-'Metrics'!$G$26&lt;=0,'Metrics'!$P$26,'Metrics'!$O$26+('Metrics'!$B$26-'Metrics'!$G$26)/('Metrics'!$H$26-'Metrics'!$G$26)*('Metrics'!$P$26-'Metrics'!$O$26)),IF('Metrics'!$B$26&lt;='Metrics'!$I$26,IF('Metrics'!$I$26-'Metrics'!$H$26&lt;=0,'Metrics'!$Q$26,'Metrics'!$P$26+('Metrics'!$B$26-'Metrics'!$H$26)/('Metrics'!$I$26-'Metrics'!$H$26)*('Metrics'!$Q$26-'Metrics'!$P$26)),IF('Metrics'!$B$26&lt;='Metrics'!$J$26,IF('Metrics'!$J$26-'Metrics'!$I$26&lt;=0,'Metrics'!$R$26,'Metrics'!$Q$26+('Metrics'!$B$26-'Metrics'!$I$26)/('Metrics'!$J$26-'Metrics'!$I$26)*('Metrics'!$R$26-'Metrics'!$Q$26)),IF('Metrics'!$B$26&lt;='Metrics'!$K$26,IF('Metrics'!$K$26-'Metrics'!$J$26&lt;=0,'Metrics'!$S$26,'Metrics'!$R$26+('Metrics'!$B$26-'Metrics'!$J$26)/('Metrics'!$K$26-'Metrics'!$J$26)*('Metrics'!$S$26-'Metrics'!$R$26)),IF('Metrics'!$B$26&lt;='Metrics'!$L$26,IF('Metrics'!$L$26-'Metrics'!$K$26&lt;=0,'Metrics'!$T$26,'Metrics'!$S$26+('Metrics'!$B$26-'Metrics'!$K$26)/('Metrics'!$L$26-'Metrics'!$K$26)*('Metrics'!$T$26-'Metrics'!$S$26)),IF('Metrics'!$M$26-'Metrics'!$L$26&lt;=0,'Metrics'!$U$26,'Metrics'!$T$26+('Metrics'!$B$26-'Metrics'!$L$26)/('Metrics'!$M$26-'Metrics'!$L$26)*('Metrics'!$U$26-'Metrics'!$T$26)))))))))))),"")</f>
         <v/>
       </c>
@@ -5398,87 +5391,87 @@
           <t>pH</t>
         </is>
       </c>
-      <c r="B27" s="76">
+      <c r="B27" s="75">
         <f>IF('DEEP Score'!$E$41="","",'DEEP Score'!$E$41)</f>
         <v/>
       </c>
-      <c r="C27" s="76">
+      <c r="C27" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D27" s="76">
+      <c r="D27" s="75">
         <f>"spring_chem_ph|"&amp;'Metrics'!$C$27</f>
         <v/>
       </c>
-      <c r="E27" s="76">
+      <c r="E27" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F27" s="76">
+      <c r="F27" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="G27" s="76">
+      <c r="G27" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="H27" s="76">
+      <c r="H27" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="I27" s="76">
+      <c r="I27" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="J27" s="76">
+      <c r="J27" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="K27" s="76">
+      <c r="K27" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="L27" s="76">
+      <c r="L27" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="M27" s="76">
+      <c r="M27" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="N27" s="76">
+      <c r="N27" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="O27" s="76">
+      <c r="O27" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="P27" s="76">
+      <c r="P27" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="Q27" s="76">
+      <c r="Q27" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="R27" s="76">
+      <c r="R27" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="S27" s="76">
+      <c r="S27" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="T27" s="76">
+      <c r="T27" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="U27" s="76">
+      <c r="U27" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$27)</f>
         <v/>
       </c>
-      <c r="V27" s="77">
+      <c r="V27" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$27),MAX(0,MIN(1,IF('Metrics'!$B$27&lt;='Metrics'!$F$27,'Metrics'!$N$27,IF('Metrics'!$B$27&gt;='Metrics'!$M$27,'Metrics'!$U$27,IF('Metrics'!$B$27&lt;='Metrics'!$G$27,IF('Metrics'!$G$27-'Metrics'!$F$27&lt;=0,'Metrics'!$O$27,'Metrics'!$N$27+('Metrics'!$B$27-'Metrics'!$F$27)/('Metrics'!$G$27-'Metrics'!$F$27)*('Metrics'!$O$27-'Metrics'!$N$27)),IF('Metrics'!$B$27&lt;='Metrics'!$H$27,IF('Metrics'!$H$27-'Metrics'!$G$27&lt;=0,'Metrics'!$P$27,'Metrics'!$O$27+('Metrics'!$B$27-'Metrics'!$G$27)/('Metrics'!$H$27-'Metrics'!$G$27)*('Metrics'!$P$27-'Metrics'!$O$27)),IF('Metrics'!$B$27&lt;='Metrics'!$I$27,IF('Metrics'!$I$27-'Metrics'!$H$27&lt;=0,'Metrics'!$Q$27,'Metrics'!$P$27+('Metrics'!$B$27-'Metrics'!$H$27)/('Metrics'!$I$27-'Metrics'!$H$27)*('Metrics'!$Q$27-'Metrics'!$P$27)),IF('Metrics'!$B$27&lt;='Metrics'!$J$27,IF('Metrics'!$J$27-'Metrics'!$I$27&lt;=0,'Metrics'!$R$27,'Metrics'!$Q$27+('Metrics'!$B$27-'Metrics'!$I$27)/('Metrics'!$J$27-'Metrics'!$I$27)*('Metrics'!$R$27-'Metrics'!$Q$27)),IF('Metrics'!$B$27&lt;='Metrics'!$K$27,IF('Metrics'!$K$27-'Metrics'!$J$27&lt;=0,'Metrics'!$S$27,'Metrics'!$R$27+('Metrics'!$B$27-'Metrics'!$J$27)/('Metrics'!$K$27-'Metrics'!$J$27)*('Metrics'!$S$27-'Metrics'!$R$27)),IF('Metrics'!$B$27&lt;='Metrics'!$L$27,IF('Metrics'!$L$27-'Metrics'!$K$27&lt;=0,'Metrics'!$T$27,'Metrics'!$S$27+('Metrics'!$B$27-'Metrics'!$K$27)/('Metrics'!$L$27-'Metrics'!$K$27)*('Metrics'!$T$27-'Metrics'!$S$27)),IF('Metrics'!$M$27-'Metrics'!$L$27&lt;=0,'Metrics'!$U$27,'Metrics'!$T$27+('Metrics'!$B$27-'Metrics'!$L$27)/('Metrics'!$M$27-'Metrics'!$L$27)*('Metrics'!$U$27-'Metrics'!$T$27)))))))))))),"")</f>
         <v/>
       </c>
@@ -5489,87 +5482,87 @@
           <t>Turbidity</t>
         </is>
       </c>
-      <c r="B28" s="76">
+      <c r="B28" s="75">
         <f>IF('DEEP Score'!$E$42="","",'DEEP Score'!$E$42)</f>
         <v/>
       </c>
-      <c r="C28" s="76">
+      <c r="C28" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D28" s="76">
+      <c r="D28" s="75">
         <f>"spring_chem_turb|"&amp;'Metrics'!$C$28</f>
         <v/>
       </c>
-      <c r="E28" s="76">
+      <c r="E28" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F28" s="76">
+      <c r="F28" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="G28" s="76">
+      <c r="G28" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="H28" s="76">
+      <c r="H28" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="I28" s="76">
+      <c r="I28" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="J28" s="76">
+      <c r="J28" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="K28" s="76">
+      <c r="K28" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="L28" s="76">
+      <c r="L28" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="M28" s="76">
+      <c r="M28" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="N28" s="76">
+      <c r="N28" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="O28" s="76">
+      <c r="O28" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="P28" s="76">
+      <c r="P28" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="Q28" s="76">
+      <c r="Q28" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="R28" s="76">
+      <c r="R28" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="S28" s="76">
+      <c r="S28" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="T28" s="76">
+      <c r="T28" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="U28" s="76">
+      <c r="U28" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$28)</f>
         <v/>
       </c>
-      <c r="V28" s="77">
+      <c r="V28" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$28),MAX(0,MIN(1,IF('Metrics'!$B$28&lt;='Metrics'!$F$28,'Metrics'!$N$28,IF('Metrics'!$B$28&gt;='Metrics'!$M$28,'Metrics'!$U$28,IF('Metrics'!$B$28&lt;='Metrics'!$G$28,IF('Metrics'!$G$28-'Metrics'!$F$28&lt;=0,'Metrics'!$O$28,'Metrics'!$N$28+('Metrics'!$B$28-'Metrics'!$F$28)/('Metrics'!$G$28-'Metrics'!$F$28)*('Metrics'!$O$28-'Metrics'!$N$28)),IF('Metrics'!$B$28&lt;='Metrics'!$H$28,IF('Metrics'!$H$28-'Metrics'!$G$28&lt;=0,'Metrics'!$P$28,'Metrics'!$O$28+('Metrics'!$B$28-'Metrics'!$G$28)/('Metrics'!$H$28-'Metrics'!$G$28)*('Metrics'!$P$28-'Metrics'!$O$28)),IF('Metrics'!$B$28&lt;='Metrics'!$I$28,IF('Metrics'!$I$28-'Metrics'!$H$28&lt;=0,'Metrics'!$Q$28,'Metrics'!$P$28+('Metrics'!$B$28-'Metrics'!$H$28)/('Metrics'!$I$28-'Metrics'!$H$28)*('Metrics'!$Q$28-'Metrics'!$P$28)),IF('Metrics'!$B$28&lt;='Metrics'!$J$28,IF('Metrics'!$J$28-'Metrics'!$I$28&lt;=0,'Metrics'!$R$28,'Metrics'!$Q$28+('Metrics'!$B$28-'Metrics'!$I$28)/('Metrics'!$J$28-'Metrics'!$I$28)*('Metrics'!$R$28-'Metrics'!$Q$28)),IF('Metrics'!$B$28&lt;='Metrics'!$K$28,IF('Metrics'!$K$28-'Metrics'!$J$28&lt;=0,'Metrics'!$S$28,'Metrics'!$R$28+('Metrics'!$B$28-'Metrics'!$J$28)/('Metrics'!$K$28-'Metrics'!$J$28)*('Metrics'!$S$28-'Metrics'!$R$28)),IF('Metrics'!$B$28&lt;='Metrics'!$L$28,IF('Metrics'!$L$28-'Metrics'!$K$28&lt;=0,'Metrics'!$T$28,'Metrics'!$S$28+('Metrics'!$B$28-'Metrics'!$K$28)/('Metrics'!$L$28-'Metrics'!$K$28)*('Metrics'!$T$28-'Metrics'!$S$28)),IF('Metrics'!$M$28-'Metrics'!$L$28&lt;=0,'Metrics'!$U$28,'Metrics'!$T$28+('Metrics'!$B$28-'Metrics'!$L$28)/('Metrics'!$M$28-'Metrics'!$L$28)*('Metrics'!$U$28-'Metrics'!$T$28)))))))))))),"")</f>
         <v/>
       </c>
@@ -5580,87 +5573,87 @@
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="B29" s="76">
+      <c r="B29" s="75">
         <f>IF('DEEP Score'!$E$43="","",'DEEP Score'!$E$43)</f>
         <v/>
       </c>
-      <c r="C29" s="76">
+      <c r="C29" s="75">
         <f>IF('DEEP Score'!$F$43="","All streams (pooled)",'DEEP Score'!$F$43)</f>
         <v/>
       </c>
-      <c r="D29" s="76">
+      <c r="D29" s="75">
         <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$29</f>
         <v/>
       </c>
-      <c r="E29" s="76">
+      <c r="E29" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_phab_pct_fast|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F29" s="76">
+      <c r="F29" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="G29" s="76">
+      <c r="G29" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="H29" s="76">
+      <c r="H29" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="I29" s="76">
+      <c r="I29" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="J29" s="76">
+      <c r="J29" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="K29" s="76">
+      <c r="K29" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="L29" s="76">
+      <c r="L29" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="M29" s="76">
+      <c r="M29" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="N29" s="76">
+      <c r="N29" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="O29" s="76">
+      <c r="O29" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="P29" s="76">
+      <c r="P29" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="Q29" s="76">
+      <c r="Q29" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="R29" s="76">
+      <c r="R29" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="S29" s="76">
+      <c r="S29" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="T29" s="76">
+      <c r="T29" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="U29" s="76">
+      <c r="U29" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$29)</f>
         <v/>
       </c>
-      <c r="V29" s="77">
+      <c r="V29" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$29),MAX(0,MIN(1,IF('Metrics'!$B$29&lt;='Metrics'!$F$29,'Metrics'!$N$29,IF('Metrics'!$B$29&gt;='Metrics'!$M$29,'Metrics'!$U$29,IF('Metrics'!$B$29&lt;='Metrics'!$G$29,IF('Metrics'!$G$29-'Metrics'!$F$29&lt;=0,'Metrics'!$O$29,'Metrics'!$N$29+('Metrics'!$B$29-'Metrics'!$F$29)/('Metrics'!$G$29-'Metrics'!$F$29)*('Metrics'!$O$29-'Metrics'!$N$29)),IF('Metrics'!$B$29&lt;='Metrics'!$H$29,IF('Metrics'!$H$29-'Metrics'!$G$29&lt;=0,'Metrics'!$P$29,'Metrics'!$O$29+('Metrics'!$B$29-'Metrics'!$G$29)/('Metrics'!$H$29-'Metrics'!$G$29)*('Metrics'!$P$29-'Metrics'!$O$29)),IF('Metrics'!$B$29&lt;='Metrics'!$I$29,IF('Metrics'!$I$29-'Metrics'!$H$29&lt;=0,'Metrics'!$Q$29,'Metrics'!$P$29+('Metrics'!$B$29-'Metrics'!$H$29)/('Metrics'!$I$29-'Metrics'!$H$29)*('Metrics'!$Q$29-'Metrics'!$P$29)),IF('Metrics'!$B$29&lt;='Metrics'!$J$29,IF('Metrics'!$J$29-'Metrics'!$I$29&lt;=0,'Metrics'!$R$29,'Metrics'!$Q$29+('Metrics'!$B$29-'Metrics'!$I$29)/('Metrics'!$J$29-'Metrics'!$I$29)*('Metrics'!$R$29-'Metrics'!$Q$29)),IF('Metrics'!$B$29&lt;='Metrics'!$K$29,IF('Metrics'!$K$29-'Metrics'!$J$29&lt;=0,'Metrics'!$S$29,'Metrics'!$R$29+('Metrics'!$B$29-'Metrics'!$J$29)/('Metrics'!$K$29-'Metrics'!$J$29)*('Metrics'!$S$29-'Metrics'!$R$29)),IF('Metrics'!$B$29&lt;='Metrics'!$L$29,IF('Metrics'!$L$29-'Metrics'!$K$29&lt;=0,'Metrics'!$T$29,'Metrics'!$S$29+('Metrics'!$B$29-'Metrics'!$K$29)/('Metrics'!$L$29-'Metrics'!$K$29)*('Metrics'!$T$29-'Metrics'!$S$29)),IF('Metrics'!$M$29-'Metrics'!$L$29&lt;=0,'Metrics'!$U$29,'Metrics'!$T$29+('Metrics'!$B$29-'Metrics'!$L$29)/('Metrics'!$M$29-'Metrics'!$L$29)*('Metrics'!$U$29-'Metrics'!$T$29)))))))))))),"")</f>
         <v/>
       </c>
@@ -5671,87 +5664,87 @@
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="B30" s="76">
+      <c r="B30" s="75">
         <f>IF('DEEP Score'!$E$44="","",'DEEP Score'!$E$44)</f>
         <v/>
       </c>
-      <c r="C30" s="76">
+      <c r="C30" s="75">
         <f>IF('DEEP Score'!$F$44="","All streams (pooled)",'DEEP Score'!$F$44)</f>
         <v/>
       </c>
-      <c r="D30" s="76">
+      <c r="D30" s="75">
         <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$30</f>
         <v/>
       </c>
-      <c r="E30" s="76">
+      <c r="E30" s="75">
         <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_phab_xfc_nat|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
-      <c r="F30" s="76">
+      <c r="F30" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="G30" s="76">
+      <c r="G30" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="H30" s="76">
+      <c r="H30" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="I30" s="76">
+      <c r="I30" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="J30" s="76">
+      <c r="J30" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="K30" s="76">
+      <c r="K30" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="L30" s="76">
+      <c r="L30" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="M30" s="76">
+      <c r="M30" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="N30" s="76">
+      <c r="N30" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="O30" s="76">
+      <c r="O30" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="P30" s="76">
+      <c r="P30" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="Q30" s="76">
+      <c r="Q30" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="R30" s="76">
+      <c r="R30" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="S30" s="76">
+      <c r="S30" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="T30" s="76">
+      <c r="T30" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="U30" s="76">
+      <c r="U30" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$30)</f>
         <v/>
       </c>
-      <c r="V30" s="77">
+      <c r="V30" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$30),MAX(0,MIN(1,IF('Metrics'!$B$30&lt;='Metrics'!$F$30,'Metrics'!$N$30,IF('Metrics'!$B$30&gt;='Metrics'!$M$30,'Metrics'!$U$30,IF('Metrics'!$B$30&lt;='Metrics'!$G$30,IF('Metrics'!$G$30-'Metrics'!$F$30&lt;=0,'Metrics'!$O$30,'Metrics'!$N$30+('Metrics'!$B$30-'Metrics'!$F$30)/('Metrics'!$G$30-'Metrics'!$F$30)*('Metrics'!$O$30-'Metrics'!$N$30)),IF('Metrics'!$B$30&lt;='Metrics'!$H$30,IF('Metrics'!$H$30-'Metrics'!$G$30&lt;=0,'Metrics'!$P$30,'Metrics'!$O$30+('Metrics'!$B$30-'Metrics'!$G$30)/('Metrics'!$H$30-'Metrics'!$G$30)*('Metrics'!$P$30-'Metrics'!$O$30)),IF('Metrics'!$B$30&lt;='Metrics'!$I$30,IF('Metrics'!$I$30-'Metrics'!$H$30&lt;=0,'Metrics'!$Q$30,'Metrics'!$P$30+('Metrics'!$B$30-'Metrics'!$H$30)/('Metrics'!$I$30-'Metrics'!$H$30)*('Metrics'!$Q$30-'Metrics'!$P$30)),IF('Metrics'!$B$30&lt;='Metrics'!$J$30,IF('Metrics'!$J$30-'Metrics'!$I$30&lt;=0,'Metrics'!$R$30,'Metrics'!$Q$30+('Metrics'!$B$30-'Metrics'!$I$30)/('Metrics'!$J$30-'Metrics'!$I$30)*('Metrics'!$R$30-'Metrics'!$Q$30)),IF('Metrics'!$B$30&lt;='Metrics'!$K$30,IF('Metrics'!$K$30-'Metrics'!$J$30&lt;=0,'Metrics'!$S$30,'Metrics'!$R$30+('Metrics'!$B$30-'Metrics'!$J$30)/('Metrics'!$K$30-'Metrics'!$J$30)*('Metrics'!$S$30-'Metrics'!$R$30)),IF('Metrics'!$B$30&lt;='Metrics'!$L$30,IF('Metrics'!$L$30-'Metrics'!$K$30&lt;=0,'Metrics'!$T$30,'Metrics'!$S$30+('Metrics'!$B$30-'Metrics'!$K$30)/('Metrics'!$L$30-'Metrics'!$K$30)*('Metrics'!$T$30-'Metrics'!$S$30)),IF('Metrics'!$M$30-'Metrics'!$L$30&lt;=0,'Metrics'!$U$30,'Metrics'!$T$30+('Metrics'!$B$30-'Metrics'!$L$30)/('Metrics'!$M$30-'Metrics'!$L$30)*('Metrics'!$U$30-'Metrics'!$T$30)))))))))))),"")</f>
         <v/>
       </c>
@@ -5759,90 +5752,90 @@
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
-        </is>
-      </c>
-      <c r="B31" s="76">
+          <t>Benthic total taxa richness</t>
+        </is>
+      </c>
+      <c r="B31" s="75">
         <f>IF('DEEP Score'!$E$45="","",'DEEP Score'!$E$45)</f>
         <v/>
       </c>
-      <c r="C31" s="76">
-        <f>IF('DEEP Score'!$F$45="","All streams (pooled)",'DEEP Score'!$F$45)</f>
-        <v/>
-      </c>
-      <c r="D31" s="76">
-        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$31</f>
-        <v/>
-      </c>
-      <c r="E31" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_fish_nat_totlntax|All streams (pooled)",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F31" s="76">
+      <c r="C31" s="75">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D31" s="75">
+        <f>"spring_bent_totlntax|"&amp;'Metrics'!$C$31</f>
+        <v/>
+      </c>
+      <c r="E31" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_bent_totlntax|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F31" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="G31" s="76">
+      <c r="G31" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="H31" s="76">
+      <c r="H31" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="I31" s="76">
+      <c r="I31" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="J31" s="76">
+      <c r="J31" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="K31" s="76">
+      <c r="K31" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="L31" s="76">
+      <c r="L31" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="M31" s="76">
+      <c r="M31" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="N31" s="76">
+      <c r="N31" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="O31" s="76">
+      <c r="O31" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="P31" s="76">
+      <c r="P31" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="Q31" s="76">
+      <c r="Q31" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="R31" s="76">
+      <c r="R31" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="S31" s="76">
+      <c r="S31" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="T31" s="76">
+      <c r="T31" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="U31" s="76">
+      <c r="U31" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$31)</f>
         <v/>
       </c>
-      <c r="V31" s="77">
+      <c r="V31" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$31),MAX(0,MIN(1,IF('Metrics'!$B$31&lt;='Metrics'!$F$31,'Metrics'!$N$31,IF('Metrics'!$B$31&gt;='Metrics'!$M$31,'Metrics'!$U$31,IF('Metrics'!$B$31&lt;='Metrics'!$G$31,IF('Metrics'!$G$31-'Metrics'!$F$31&lt;=0,'Metrics'!$O$31,'Metrics'!$N$31+('Metrics'!$B$31-'Metrics'!$F$31)/('Metrics'!$G$31-'Metrics'!$F$31)*('Metrics'!$O$31-'Metrics'!$N$31)),IF('Metrics'!$B$31&lt;='Metrics'!$H$31,IF('Metrics'!$H$31-'Metrics'!$G$31&lt;=0,'Metrics'!$P$31,'Metrics'!$O$31+('Metrics'!$B$31-'Metrics'!$G$31)/('Metrics'!$H$31-'Metrics'!$G$31)*('Metrics'!$P$31-'Metrics'!$O$31)),IF('Metrics'!$B$31&lt;='Metrics'!$I$31,IF('Metrics'!$I$31-'Metrics'!$H$31&lt;=0,'Metrics'!$Q$31,'Metrics'!$P$31+('Metrics'!$B$31-'Metrics'!$H$31)/('Metrics'!$I$31-'Metrics'!$H$31)*('Metrics'!$Q$31-'Metrics'!$P$31)),IF('Metrics'!$B$31&lt;='Metrics'!$J$31,IF('Metrics'!$J$31-'Metrics'!$I$31&lt;=0,'Metrics'!$R$31,'Metrics'!$Q$31+('Metrics'!$B$31-'Metrics'!$I$31)/('Metrics'!$J$31-'Metrics'!$I$31)*('Metrics'!$R$31-'Metrics'!$Q$31)),IF('Metrics'!$B$31&lt;='Metrics'!$K$31,IF('Metrics'!$K$31-'Metrics'!$J$31&lt;=0,'Metrics'!$S$31,'Metrics'!$R$31+('Metrics'!$B$31-'Metrics'!$J$31)/('Metrics'!$K$31-'Metrics'!$J$31)*('Metrics'!$S$31-'Metrics'!$R$31)),IF('Metrics'!$B$31&lt;='Metrics'!$L$31,IF('Metrics'!$L$31-'Metrics'!$K$31&lt;=0,'Metrics'!$T$31,'Metrics'!$S$31+('Metrics'!$B$31-'Metrics'!$K$31)/('Metrics'!$L$31-'Metrics'!$K$31)*('Metrics'!$T$31-'Metrics'!$S$31)),IF('Metrics'!$M$31-'Metrics'!$L$31&lt;=0,'Metrics'!$U$31,'Metrics'!$T$31+('Metrics'!$B$31-'Metrics'!$L$31)/('Metrics'!$M$31-'Metrics'!$L$31)*('Metrics'!$U$31-'Metrics'!$T$31)))))))))))),"")</f>
         <v/>
       </c>
@@ -5850,90 +5843,90 @@
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
-        </is>
-      </c>
-      <c r="B32" s="76">
+          <t>Native fish taxa richness</t>
+        </is>
+      </c>
+      <c r="B32" s="75">
         <f>IF('DEEP Score'!$E$46="","",'DEEP Score'!$E$46)</f>
         <v/>
       </c>
-      <c r="C32" s="76">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D32" s="76">
-        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$32</f>
-        <v/>
-      </c>
-      <c r="E32" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F32" s="76">
+      <c r="C32" s="75">
+        <f>IF('DEEP Score'!$F$46="","All streams (pooled)",'DEEP Score'!$F$46)</f>
+        <v/>
+      </c>
+      <c r="D32" s="75">
+        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$32</f>
+        <v/>
+      </c>
+      <c r="E32" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_fish_nat_totlntax|All streams (pooled)",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F32" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="H32" s="76">
+      <c r="H32" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="I32" s="76">
+      <c r="I32" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="J32" s="76">
+      <c r="J32" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="K32" s="76">
+      <c r="K32" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="L32" s="76">
+      <c r="L32" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="M32" s="76">
+      <c r="M32" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="N32" s="76">
+      <c r="N32" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="O32" s="76">
+      <c r="O32" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="P32" s="76">
+      <c r="P32" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="Q32" s="76">
+      <c r="Q32" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="R32" s="76">
+      <c r="R32" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="S32" s="76">
+      <c r="S32" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="T32" s="76">
+      <c r="T32" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="U32" s="76">
+      <c r="U32" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$32)</f>
         <v/>
       </c>
-      <c r="V32" s="77">
+      <c r="V32" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$32),MAX(0,MIN(1,IF('Metrics'!$B$32&lt;='Metrics'!$F$32,'Metrics'!$N$32,IF('Metrics'!$B$32&gt;='Metrics'!$M$32,'Metrics'!$U$32,IF('Metrics'!$B$32&lt;='Metrics'!$G$32,IF('Metrics'!$G$32-'Metrics'!$F$32&lt;=0,'Metrics'!$O$32,'Metrics'!$N$32+('Metrics'!$B$32-'Metrics'!$F$32)/('Metrics'!$G$32-'Metrics'!$F$32)*('Metrics'!$O$32-'Metrics'!$N$32)),IF('Metrics'!$B$32&lt;='Metrics'!$H$32,IF('Metrics'!$H$32-'Metrics'!$G$32&lt;=0,'Metrics'!$P$32,'Metrics'!$O$32+('Metrics'!$B$32-'Metrics'!$G$32)/('Metrics'!$H$32-'Metrics'!$G$32)*('Metrics'!$P$32-'Metrics'!$O$32)),IF('Metrics'!$B$32&lt;='Metrics'!$I$32,IF('Metrics'!$I$32-'Metrics'!$H$32&lt;=0,'Metrics'!$Q$32,'Metrics'!$P$32+('Metrics'!$B$32-'Metrics'!$H$32)/('Metrics'!$I$32-'Metrics'!$H$32)*('Metrics'!$Q$32-'Metrics'!$P$32)),IF('Metrics'!$B$32&lt;='Metrics'!$J$32,IF('Metrics'!$J$32-'Metrics'!$I$32&lt;=0,'Metrics'!$R$32,'Metrics'!$Q$32+('Metrics'!$B$32-'Metrics'!$I$32)/('Metrics'!$J$32-'Metrics'!$I$32)*('Metrics'!$R$32-'Metrics'!$Q$32)),IF('Metrics'!$B$32&lt;='Metrics'!$K$32,IF('Metrics'!$K$32-'Metrics'!$J$32&lt;=0,'Metrics'!$S$32,'Metrics'!$R$32+('Metrics'!$B$32-'Metrics'!$J$32)/('Metrics'!$K$32-'Metrics'!$J$32)*('Metrics'!$S$32-'Metrics'!$R$32)),IF('Metrics'!$B$32&lt;='Metrics'!$L$32,IF('Metrics'!$L$32-'Metrics'!$K$32&lt;=0,'Metrics'!$T$32,'Metrics'!$S$32+('Metrics'!$B$32-'Metrics'!$K$32)/('Metrics'!$L$32-'Metrics'!$K$32)*('Metrics'!$T$32-'Metrics'!$S$32)),IF('Metrics'!$M$32-'Metrics'!$L$32&lt;=0,'Metrics'!$U$32,'Metrics'!$T$32+('Metrics'!$B$32-'Metrics'!$L$32)/('Metrics'!$M$32-'Metrics'!$L$32)*('Metrics'!$U$32-'Metrics'!$T$32)))))))))))),"")</f>
         <v/>
       </c>
@@ -5941,90 +5934,90 @@
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
-        </is>
-      </c>
-      <c r="B33" s="76">
+          <t>EPT taxa richness</t>
+        </is>
+      </c>
+      <c r="B33" s="75">
         <f>IF('DEEP Score'!$E$47="","",'DEEP Score'!$E$47)</f>
         <v/>
       </c>
-      <c r="C33" s="76">
+      <c r="C33" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D33" s="76">
-        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$33</f>
-        <v/>
-      </c>
-      <c r="E33" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F33" s="76">
+      <c r="D33" s="75">
+        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$33</f>
+        <v/>
+      </c>
+      <c r="E33" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F33" s="75">
         <f>INDEX(curve_x1,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="G33" s="76">
+      <c r="G33" s="75">
         <f>INDEX(curve_x2,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="H33" s="76">
+      <c r="H33" s="75">
         <f>INDEX(curve_x3,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="I33" s="76">
+      <c r="I33" s="75">
         <f>INDEX(curve_x4,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="J33" s="76">
+      <c r="J33" s="75">
         <f>INDEX(curve_x5,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="K33" s="76">
+      <c r="K33" s="75">
         <f>INDEX(curve_x6,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="L33" s="76">
+      <c r="L33" s="75">
         <f>INDEX(curve_x7,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="M33" s="76">
+      <c r="M33" s="75">
         <f>INDEX(curve_x8,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="N33" s="76">
+      <c r="N33" s="75">
         <f>INDEX(curve_y1,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="O33" s="76">
+      <c r="O33" s="75">
         <f>INDEX(curve_y2,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="P33" s="76">
+      <c r="P33" s="75">
         <f>INDEX(curve_y3,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="Q33" s="76">
+      <c r="Q33" s="75">
         <f>INDEX(curve_y4,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="R33" s="76">
+      <c r="R33" s="75">
         <f>INDEX(curve_y5,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="S33" s="76">
+      <c r="S33" s="75">
         <f>INDEX(curve_y6,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="T33" s="76">
+      <c r="T33" s="75">
         <f>INDEX(curve_y7,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="U33" s="76">
+      <c r="U33" s="75">
         <f>INDEX(curve_y8,'Metrics'!$E$33)</f>
         <v/>
       </c>
-      <c r="V33" s="77">
+      <c r="V33" s="76">
         <f>IF(ISNUMBER('Metrics'!$B$33),MAX(0,MIN(1,IF('Metrics'!$B$33&lt;='Metrics'!$F$33,'Metrics'!$N$33,IF('Metrics'!$B$33&gt;='Metrics'!$M$33,'Metrics'!$U$33,IF('Metrics'!$B$33&lt;='Metrics'!$G$33,IF('Metrics'!$G$33-'Metrics'!$F$33&lt;=0,'Metrics'!$O$33,'Metrics'!$N$33+('Metrics'!$B$33-'Metrics'!$F$33)/('Metrics'!$G$33-'Metrics'!$F$33)*('Metrics'!$O$33-'Metrics'!$N$33)),IF('Metrics'!$B$33&lt;='Metrics'!$H$33,IF('Metrics'!$H$33-'Metrics'!$G$33&lt;=0,'Metrics'!$P$33,'Metrics'!$O$33+('Metrics'!$B$33-'Metrics'!$G$33)/('Metrics'!$H$33-'Metrics'!$G$33)*('Metrics'!$P$33-'Metrics'!$O$33)),IF('Metrics'!$B$33&lt;='Metrics'!$I$33,IF('Metrics'!$I$33-'Metrics'!$H$33&lt;=0,'Metrics'!$Q$33,'Metrics'!$P$33+('Metrics'!$B$33-'Metrics'!$H$33)/('Metrics'!$I$33-'Metrics'!$H$33)*('Metrics'!$Q$33-'Metrics'!$P$33)),IF('Metrics'!$B$33&lt;='Metrics'!$J$33,IF('Metrics'!$J$33-'Metrics'!$I$33&lt;=0,'Metrics'!$R$33,'Metrics'!$Q$33+('Metrics'!$B$33-'Metrics'!$I$33)/('Metrics'!$J$33-'Metrics'!$I$33)*('Metrics'!$R$33-'Metrics'!$Q$33)),IF('Metrics'!$B$33&lt;='Metrics'!$K$33,IF('Metrics'!$K$33-'Metrics'!$J$33&lt;=0,'Metrics'!$S$33,'Metrics'!$R$33+('Metrics'!$B$33-'Metrics'!$J$33)/('Metrics'!$K$33-'Metrics'!$J$33)*('Metrics'!$S$33-'Metrics'!$R$33)),IF('Metrics'!$B$33&lt;='Metrics'!$L$33,IF('Metrics'!$L$33-'Metrics'!$K$33&lt;=0,'Metrics'!$T$33,'Metrics'!$S$33+('Metrics'!$B$33-'Metrics'!$K$33)/('Metrics'!$L$33-'Metrics'!$K$33)*('Metrics'!$T$33-'Metrics'!$S$33)),IF('Metrics'!$M$33-'Metrics'!$L$33&lt;=0,'Metrics'!$U$33,'Metrics'!$T$33+('Metrics'!$B$33-'Metrics'!$L$33)/('Metrics'!$M$33-'Metrics'!$L$33)*('Metrics'!$U$33-'Metrics'!$T$33)))))))))))),"")</f>
         <v/>
       </c>
@@ -6032,91 +6025,182 @@
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
         <is>
+          <t>Shannon diversity (H')</t>
+        </is>
+      </c>
+      <c r="B34" s="75">
+        <f>IF('DEEP Score'!$E$48="","",'DEEP Score'!$E$48)</f>
+        <v/>
+      </c>
+      <c r="C34" s="75">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D34" s="75">
+        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$34</f>
+        <v/>
+      </c>
+      <c r="E34" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$34,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F34" s="75">
+        <f>INDEX(curve_x1,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="75">
+        <f>INDEX(curve_x2,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="75">
+        <f>INDEX(curve_x3,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="75">
+        <f>INDEX(curve_x4,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="75">
+        <f>INDEX(curve_x5,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="75">
+        <f>INDEX(curve_x6,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="75">
+        <f>INDEX(curve_x7,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="75">
+        <f>INDEX(curve_x8,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="75">
+        <f>INDEX(curve_y1,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="75">
+        <f>INDEX(curve_y2,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="75">
+        <f>INDEX(curve_y3,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="75">
+        <f>INDEX(curve_y4,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="R34" s="75">
+        <f>INDEX(curve_y5,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="S34" s="75">
+        <f>INDEX(curve_y6,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="75">
+        <f>INDEX(curve_y7,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="75">
+        <f>INDEX(curve_y8,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="V34" s="76">
+        <f>IF(ISNUMBER('Metrics'!$B$34),MAX(0,MIN(1,IF('Metrics'!$B$34&lt;='Metrics'!$F$34,'Metrics'!$N$34,IF('Metrics'!$B$34&gt;='Metrics'!$M$34,'Metrics'!$U$34,IF('Metrics'!$B$34&lt;='Metrics'!$G$34,IF('Metrics'!$G$34-'Metrics'!$F$34&lt;=0,'Metrics'!$O$34,'Metrics'!$N$34+('Metrics'!$B$34-'Metrics'!$F$34)/('Metrics'!$G$34-'Metrics'!$F$34)*('Metrics'!$O$34-'Metrics'!$N$34)),IF('Metrics'!$B$34&lt;='Metrics'!$H$34,IF('Metrics'!$H$34-'Metrics'!$G$34&lt;=0,'Metrics'!$P$34,'Metrics'!$O$34+('Metrics'!$B$34-'Metrics'!$G$34)/('Metrics'!$H$34-'Metrics'!$G$34)*('Metrics'!$P$34-'Metrics'!$O$34)),IF('Metrics'!$B$34&lt;='Metrics'!$I$34,IF('Metrics'!$I$34-'Metrics'!$H$34&lt;=0,'Metrics'!$Q$34,'Metrics'!$P$34+('Metrics'!$B$34-'Metrics'!$H$34)/('Metrics'!$I$34-'Metrics'!$H$34)*('Metrics'!$Q$34-'Metrics'!$P$34)),IF('Metrics'!$B$34&lt;='Metrics'!$J$34,IF('Metrics'!$J$34-'Metrics'!$I$34&lt;=0,'Metrics'!$R$34,'Metrics'!$Q$34+('Metrics'!$B$34-'Metrics'!$I$34)/('Metrics'!$J$34-'Metrics'!$I$34)*('Metrics'!$R$34-'Metrics'!$Q$34)),IF('Metrics'!$B$34&lt;='Metrics'!$K$34,IF('Metrics'!$K$34-'Metrics'!$J$34&lt;=0,'Metrics'!$S$34,'Metrics'!$R$34+('Metrics'!$B$34-'Metrics'!$J$34)/('Metrics'!$K$34-'Metrics'!$J$34)*('Metrics'!$S$34-'Metrics'!$R$34)),IF('Metrics'!$B$34&lt;='Metrics'!$L$34,IF('Metrics'!$L$34-'Metrics'!$K$34&lt;=0,'Metrics'!$T$34,'Metrics'!$S$34+('Metrics'!$B$34-'Metrics'!$K$34)/('Metrics'!$L$34-'Metrics'!$K$34)*('Metrics'!$T$34-'Metrics'!$S$34)),IF('Metrics'!$M$34-'Metrics'!$L$34&lt;=0,'Metrics'!$U$34,'Metrics'!$T$34+('Metrics'!$B$34-'Metrics'!$L$34)/('Metrics'!$M$34-'Metrics'!$L$34)*('Metrics'!$U$34-'Metrics'!$T$34)))))))))))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="B34" s="76">
-        <f>IF('DEEP Score'!$E$48="","",'DEEP Score'!$E$48)</f>
-        <v/>
-      </c>
-      <c r="C34" s="76">
+      <c r="B35" s="75">
+        <f>IF('DEEP Score'!$E$49="","",'DEEP Score'!$E$49)</f>
+        <v/>
+      </c>
+      <c r="C35" s="75">
         <f>""</f>
         <v/>
       </c>
-      <c r="D34" s="76">
-        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$34</f>
-        <v/>
-      </c>
-      <c r="E34" s="76">
-        <f>IFERROR(MATCH('Metrics'!$D$34,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F34" s="76">
-        <f>INDEX(curve_x1,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="76">
-        <f>INDEX(curve_x2,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="76">
-        <f>INDEX(curve_x3,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="76">
-        <f>INDEX(curve_x4,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="76">
-        <f>INDEX(curve_x5,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="76">
-        <f>INDEX(curve_x6,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="76">
-        <f>INDEX(curve_x7,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="76">
-        <f>INDEX(curve_x8,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="76">
-        <f>INDEX(curve_y1,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="76">
-        <f>INDEX(curve_y2,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="P34" s="76">
-        <f>INDEX(curve_y3,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="76">
-        <f>INDEX(curve_y4,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="R34" s="76">
-        <f>INDEX(curve_y5,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="S34" s="76">
-        <f>INDEX(curve_y6,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="T34" s="76">
-        <f>INDEX(curve_y7,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="U34" s="76">
-        <f>INDEX(curve_y8,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="V34" s="77">
-        <f>IF(ISNUMBER('Metrics'!$B$34),MAX(0,MIN(1,IF('Metrics'!$B$34&lt;='Metrics'!$F$34,'Metrics'!$N$34,IF('Metrics'!$B$34&gt;='Metrics'!$M$34,'Metrics'!$U$34,IF('Metrics'!$B$34&lt;='Metrics'!$G$34,IF('Metrics'!$G$34-'Metrics'!$F$34&lt;=0,'Metrics'!$O$34,'Metrics'!$N$34+('Metrics'!$B$34-'Metrics'!$F$34)/('Metrics'!$G$34-'Metrics'!$F$34)*('Metrics'!$O$34-'Metrics'!$N$34)),IF('Metrics'!$B$34&lt;='Metrics'!$H$34,IF('Metrics'!$H$34-'Metrics'!$G$34&lt;=0,'Metrics'!$P$34,'Metrics'!$O$34+('Metrics'!$B$34-'Metrics'!$G$34)/('Metrics'!$H$34-'Metrics'!$G$34)*('Metrics'!$P$34-'Metrics'!$O$34)),IF('Metrics'!$B$34&lt;='Metrics'!$I$34,IF('Metrics'!$I$34-'Metrics'!$H$34&lt;=0,'Metrics'!$Q$34,'Metrics'!$P$34+('Metrics'!$B$34-'Metrics'!$H$34)/('Metrics'!$I$34-'Metrics'!$H$34)*('Metrics'!$Q$34-'Metrics'!$P$34)),IF('Metrics'!$B$34&lt;='Metrics'!$J$34,IF('Metrics'!$J$34-'Metrics'!$I$34&lt;=0,'Metrics'!$R$34,'Metrics'!$Q$34+('Metrics'!$B$34-'Metrics'!$I$34)/('Metrics'!$J$34-'Metrics'!$I$34)*('Metrics'!$R$34-'Metrics'!$Q$34)),IF('Metrics'!$B$34&lt;='Metrics'!$K$34,IF('Metrics'!$K$34-'Metrics'!$J$34&lt;=0,'Metrics'!$S$34,'Metrics'!$R$34+('Metrics'!$B$34-'Metrics'!$J$34)/('Metrics'!$K$34-'Metrics'!$J$34)*('Metrics'!$S$34-'Metrics'!$R$34)),IF('Metrics'!$B$34&lt;='Metrics'!$L$34,IF('Metrics'!$L$34-'Metrics'!$K$34&lt;=0,'Metrics'!$T$34,'Metrics'!$S$34+('Metrics'!$B$34-'Metrics'!$K$34)/('Metrics'!$L$34-'Metrics'!$K$34)*('Metrics'!$T$34-'Metrics'!$S$34)),IF('Metrics'!$M$34-'Metrics'!$L$34&lt;=0,'Metrics'!$U$34,'Metrics'!$T$34+('Metrics'!$B$34-'Metrics'!$L$34)/('Metrics'!$M$34-'Metrics'!$L$34)*('Metrics'!$U$34-'Metrics'!$T$34)))))))))))),"")</f>
+      <c r="D35" s="75">
+        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$35</f>
+        <v/>
+      </c>
+      <c r="E35" s="75">
+        <f>IFERROR(MATCH('Metrics'!$D$35,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F35" s="75">
+        <f>INDEX(curve_x1,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="75">
+        <f>INDEX(curve_x2,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="75">
+        <f>INDEX(curve_x3,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="75">
+        <f>INDEX(curve_x4,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="75">
+        <f>INDEX(curve_x5,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="75">
+        <f>INDEX(curve_x6,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="75">
+        <f>INDEX(curve_x7,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="75">
+        <f>INDEX(curve_x8,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="75">
+        <f>INDEX(curve_y1,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="75">
+        <f>INDEX(curve_y2,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="75">
+        <f>INDEX(curve_y3,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="75">
+        <f>INDEX(curve_y4,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="R35" s="75">
+        <f>INDEX(curve_y5,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="S35" s="75">
+        <f>INDEX(curve_y6,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="T35" s="75">
+        <f>INDEX(curve_y7,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="U35" s="75">
+        <f>INDEX(curve_y8,'Metrics'!$E$35)</f>
+        <v/>
+      </c>
+      <c r="V35" s="76">
+        <f>IF(ISNUMBER('Metrics'!$B$35),MAX(0,MIN(1,IF('Metrics'!$B$35&lt;='Metrics'!$F$35,'Metrics'!$N$35,IF('Metrics'!$B$35&gt;='Metrics'!$M$35,'Metrics'!$U$35,IF('Metrics'!$B$35&lt;='Metrics'!$G$35,IF('Metrics'!$G$35-'Metrics'!$F$35&lt;=0,'Metrics'!$O$35,'Metrics'!$N$35+('Metrics'!$B$35-'Metrics'!$F$35)/('Metrics'!$G$35-'Metrics'!$F$35)*('Metrics'!$O$35-'Metrics'!$N$35)),IF('Metrics'!$B$35&lt;='Metrics'!$H$35,IF('Metrics'!$H$35-'Metrics'!$G$35&lt;=0,'Metrics'!$P$35,'Metrics'!$O$35+('Metrics'!$B$35-'Metrics'!$G$35)/('Metrics'!$H$35-'Metrics'!$G$35)*('Metrics'!$P$35-'Metrics'!$O$35)),IF('Metrics'!$B$35&lt;='Metrics'!$I$35,IF('Metrics'!$I$35-'Metrics'!$H$35&lt;=0,'Metrics'!$Q$35,'Metrics'!$P$35+('Metrics'!$B$35-'Metrics'!$H$35)/('Metrics'!$I$35-'Metrics'!$H$35)*('Metrics'!$Q$35-'Metrics'!$P$35)),IF('Metrics'!$B$35&lt;='Metrics'!$J$35,IF('Metrics'!$J$35-'Metrics'!$I$35&lt;=0,'Metrics'!$R$35,'Metrics'!$Q$35+('Metrics'!$B$35-'Metrics'!$I$35)/('Metrics'!$J$35-'Metrics'!$I$35)*('Metrics'!$R$35-'Metrics'!$Q$35)),IF('Metrics'!$B$35&lt;='Metrics'!$K$35,IF('Metrics'!$K$35-'Metrics'!$J$35&lt;=0,'Metrics'!$S$35,'Metrics'!$R$35+('Metrics'!$B$35-'Metrics'!$J$35)/('Metrics'!$K$35-'Metrics'!$J$35)*('Metrics'!$S$35-'Metrics'!$R$35)),IF('Metrics'!$B$35&lt;='Metrics'!$L$35,IF('Metrics'!$L$35-'Metrics'!$K$35&lt;=0,'Metrics'!$T$35,'Metrics'!$S$35+('Metrics'!$B$35-'Metrics'!$K$35)/('Metrics'!$L$35-'Metrics'!$K$35)*('Metrics'!$T$35-'Metrics'!$S$35)),IF('Metrics'!$M$35-'Metrics'!$L$35&lt;=0,'Metrics'!$U$35,'Metrics'!$T$35+('Metrics'!$B$35-'Metrics'!$L$35)/('Metrics'!$M$35-'Metrics'!$L$35)*('Metrics'!$U$35-'Metrics'!$T$35)))))))))))),"")</f>
         <v/>
       </c>
     </row>
@@ -6139,7 +6223,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Function scores and the outcome rollup</t>
         </is>
@@ -6208,7 +6292,7 @@
           <t>Catchment hydrology</t>
         </is>
       </c>
-      <c r="B4" s="76">
+      <c r="B4" s="75">
         <f>IF(COUNT('DEEP Score'!G12:G13)=0,"",SUM('DEEP Score'!G12:G13)/COUNT('DEEP Score'!G12:G13)*15)</f>
         <v/>
       </c>
@@ -6221,27 +6305,27 @@
       <c r="E4" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$C$4,0)</f>
         <v/>
       </c>
-      <c r="G4" s="76">
+      <c r="G4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$D$4,0)</f>
         <v/>
       </c>
-      <c r="H4" s="76">
+      <c r="H4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),'Results'!$B$4*'Results'!$E$4,0)</f>
         <v/>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$C$4,0)</f>
         <v/>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$D$4,0)</f>
         <v/>
       </c>
-      <c r="K4" s="76">
+      <c r="K4" s="75">
         <f>IF(ISNUMBER('Results'!$B$4),15*'Results'!$E$4,0)</f>
         <v/>
       </c>
@@ -6252,7 +6336,7 @@
           <t>Surface water storage</t>
         </is>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="75">
         <f>IF(COUNT('DEEP Score'!G14:G14)=0,"",SUM('DEEP Score'!G14:G14)/COUNT('DEEP Score'!G14:G14)*15)</f>
         <v/>
       </c>
@@ -6265,27 +6349,27 @@
       <c r="E5" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$C$5,0)</f>
         <v/>
       </c>
-      <c r="G5" s="76">
+      <c r="G5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$D$5,0)</f>
         <v/>
       </c>
-      <c r="H5" s="76">
+      <c r="H5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),'Results'!$B$5*'Results'!$E$5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$C$5,0)</f>
         <v/>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$D$5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="76">
+      <c r="K5" s="75">
         <f>IF(ISNUMBER('Results'!$B$5),15*'Results'!$E$5,0)</f>
         <v/>
       </c>
@@ -6296,7 +6380,7 @@
           <t>Reach inflow</t>
         </is>
       </c>
-      <c r="B6" s="76">
+      <c r="B6" s="75">
         <f>IF(COUNT('DEEP Score'!G15:G15)=0,"",SUM('DEEP Score'!G15:G15)/COUNT('DEEP Score'!G15:G15)*15)</f>
         <v/>
       </c>
@@ -6309,27 +6393,27 @@
       <c r="E6" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="G6" s="76">
+      <c r="G6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$D$6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),'Results'!$B$6*'Results'!$E$6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$D$6,0)</f>
         <v/>
       </c>
-      <c r="K6" s="76">
+      <c r="K6" s="75">
         <f>IF(ISNUMBER('Results'!$B$6),15*'Results'!$E$6,0)</f>
         <v/>
       </c>
@@ -6340,7 +6424,7 @@
           <t>Streamflow regime</t>
         </is>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="75">
         <f>IF(COUNT('DEEP Score'!G16:G17)=0,"",SUM('DEEP Score'!G16:G17)/COUNT('DEEP Score'!G16:G17)*15)</f>
         <v/>
       </c>
@@ -6353,27 +6437,27 @@
       <c r="E7" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$C$7,0)</f>
         <v/>
       </c>
-      <c r="G7" s="76">
+      <c r="G7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$D$7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),'Results'!$B$7*'Results'!$E$7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$C$7,0)</f>
         <v/>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$D$7,0)</f>
         <v/>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="75">
         <f>IF(ISNUMBER('Results'!$B$7),15*'Results'!$E$7,0)</f>
         <v/>
       </c>
@@ -6384,7 +6468,7 @@
           <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
-      <c r="B8" s="76">
+      <c r="B8" s="75">
         <f>IF(COUNT('DEEP Score'!G18:G20)=0,"",SUM('DEEP Score'!G18:G20)/COUNT('DEEP Score'!G18:G20)*15)</f>
         <v/>
       </c>
@@ -6397,27 +6481,27 @@
       <c r="E8" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$D$8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),'Results'!$B$8*'Results'!$E$8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$C$8,0)</f>
         <v/>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$D$8,0)</f>
         <v/>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="75">
         <f>IF(ISNUMBER('Results'!$B$8),15*'Results'!$E$8,0)</f>
         <v/>
       </c>
@@ -6428,7 +6512,7 @@
           <t>High flow dynamics</t>
         </is>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="75">
         <f>IF(COUNT('DEEP Score'!G21:G21)=0,"",SUM('DEEP Score'!G21:G21)/COUNT('DEEP Score'!G21:G21)*15)</f>
         <v/>
       </c>
@@ -6441,27 +6525,27 @@
       <c r="E9" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$C$9,0)</f>
         <v/>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$D$9,0)</f>
         <v/>
       </c>
-      <c r="H9" s="76">
+      <c r="H9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),'Results'!$B$9*'Results'!$E$9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$C$9,0)</f>
         <v/>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$D$9,0)</f>
         <v/>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="75">
         <f>IF(ISNUMBER('Results'!$B$9),15*'Results'!$E$9,0)</f>
         <v/>
       </c>
@@ -6472,7 +6556,7 @@
           <t>Floodplain connectivity</t>
         </is>
       </c>
-      <c r="B10" s="76">
+      <c r="B10" s="75">
         <f>IF(COUNT('DEEP Score'!G22:G23)=0,"",SUM('DEEP Score'!G22:G23)/COUNT('DEEP Score'!G22:G23)*15)</f>
         <v/>
       </c>
@@ -6485,27 +6569,27 @@
       <c r="E10" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$D$10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),'Results'!$B$10*'Results'!$E$10,0)</f>
         <v/>
       </c>
-      <c r="I10" s="76">
+      <c r="I10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$D$10,0)</f>
         <v/>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="75">
         <f>IF(ISNUMBER('Results'!$B$10),15*'Results'!$E$10,0)</f>
         <v/>
       </c>
@@ -6516,7 +6600,7 @@
           <t>Hyporheic connectivity</t>
         </is>
       </c>
-      <c r="B11" s="76">
+      <c r="B11" s="75">
         <f>IF(COUNT('DEEP Score'!G24:G25)=0,"",SUM('DEEP Score'!G24:G25)/COUNT('DEEP Score'!G24:G25)*15)</f>
         <v/>
       </c>
@@ -6529,27 +6613,27 @@
       <c r="E11" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$C$11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="76">
+      <c r="G11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$D$11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="76">
+      <c r="H11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),'Results'!$B$11*'Results'!$E$11,0)</f>
         <v/>
       </c>
-      <c r="I11" s="76">
+      <c r="I11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$C$11,0)</f>
         <v/>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$D$11,0)</f>
         <v/>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="75">
         <f>IF(ISNUMBER('Results'!$B$11),15*'Results'!$E$11,0)</f>
         <v/>
       </c>
@@ -6560,7 +6644,7 @@
           <t>Channel evolution</t>
         </is>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="75">
         <f>IF(COUNT('DEEP Score'!G26:G27)=0,"",SUM('DEEP Score'!G26:G27)/COUNT('DEEP Score'!G26:G27)*15)</f>
         <v/>
       </c>
@@ -6573,27 +6657,27 @@
       <c r="E12" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F12" s="76">
+      <c r="F12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$C$12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="76">
+      <c r="G12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$D$12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),'Results'!$B$12*'Results'!$E$12,0)</f>
         <v/>
       </c>
-      <c r="I12" s="76">
+      <c r="I12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$C$12,0)</f>
         <v/>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$D$12,0)</f>
         <v/>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="75">
         <f>IF(ISNUMBER('Results'!$B$12),15*'Results'!$E$12,0)</f>
         <v/>
       </c>
@@ -6604,7 +6688,7 @@
           <t>Channel and floodplain dynamics</t>
         </is>
       </c>
-      <c r="B13" s="76">
+      <c r="B13" s="75">
         <f>IF(COUNT('DEEP Score'!G28:G29)=0,"",SUM('DEEP Score'!G28:G29)/COUNT('DEEP Score'!G28:G29)*15)</f>
         <v/>
       </c>
@@ -6617,27 +6701,27 @@
       <c r="E13" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$C$13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$D$13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),'Results'!$B$13*'Results'!$E$13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="76">
+      <c r="I13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$C$13,0)</f>
         <v/>
       </c>
-      <c r="J13" s="76">
+      <c r="J13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$D$13,0)</f>
         <v/>
       </c>
-      <c r="K13" s="76">
+      <c r="K13" s="75">
         <f>IF(ISNUMBER('Results'!$B$13),15*'Results'!$E$13,0)</f>
         <v/>
       </c>
@@ -6648,7 +6732,7 @@
           <t>Sediment continuity</t>
         </is>
       </c>
-      <c r="B14" s="76">
+      <c r="B14" s="75">
         <f>IF(COUNT('DEEP Score'!G30:G31)=0,"",SUM('DEEP Score'!G30:G31)/COUNT('DEEP Score'!G30:G31)*15)</f>
         <v/>
       </c>
@@ -6661,27 +6745,27 @@
       <c r="E14" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$C$14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$D$14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),'Results'!$B$14*'Results'!$E$14,0)</f>
         <v/>
       </c>
-      <c r="I14" s="76">
+      <c r="I14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$C$14,0)</f>
         <v/>
       </c>
-      <c r="J14" s="76">
+      <c r="J14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$D$14,0)</f>
         <v/>
       </c>
-      <c r="K14" s="76">
+      <c r="K14" s="75">
         <f>IF(ISNUMBER('Results'!$B$14),15*'Results'!$E$14,0)</f>
         <v/>
       </c>
@@ -6692,7 +6776,7 @@
           <t>Bed composition and bedform dynamics</t>
         </is>
       </c>
-      <c r="B15" s="76">
+      <c r="B15" s="75">
         <f>IF(COUNT('DEEP Score'!G32:G34)=0,"",SUM('DEEP Score'!G32:G34)/COUNT('DEEP Score'!G32:G34)*15)</f>
         <v/>
       </c>
@@ -6705,27 +6789,27 @@
       <c r="E15" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$D$15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="76">
+      <c r="H15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),'Results'!$B$15*'Results'!$E$15,0)</f>
         <v/>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$D$15,0)</f>
         <v/>
       </c>
-      <c r="K15" s="76">
+      <c r="K15" s="75">
         <f>IF(ISNUMBER('Results'!$B$15),15*'Results'!$E$15,0)</f>
         <v/>
       </c>
@@ -6736,7 +6820,7 @@
           <t>Light &amp; thermal regime</t>
         </is>
       </c>
-      <c r="B16" s="76">
+      <c r="B16" s="75">
         <f>IF(COUNT('DEEP Score'!G35:G36)=0,"",SUM('DEEP Score'!G35:G36)/COUNT('DEEP Score'!G35:G36)*15)</f>
         <v/>
       </c>
@@ -6749,27 +6833,27 @@
       <c r="E16" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="76">
+      <c r="F16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$D$16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),'Results'!$B$16*'Results'!$E$16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="76">
+      <c r="I16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="J16" s="76">
+      <c r="J16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$D$16,0)</f>
         <v/>
       </c>
-      <c r="K16" s="76">
+      <c r="K16" s="75">
         <f>IF(ISNUMBER('Results'!$B$16),15*'Results'!$E$16,0)</f>
         <v/>
       </c>
@@ -6780,7 +6864,7 @@
           <t>Carbon processing</t>
         </is>
       </c>
-      <c r="B17" s="76">
+      <c r="B17" s="75">
         <f>IF(COUNT('DEEP Score'!G37:G37)=0,"",SUM('DEEP Score'!G37:G37)/COUNT('DEEP Score'!G37:G37)*15)</f>
         <v/>
       </c>
@@ -6793,27 +6877,27 @@
       <c r="E17" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="76">
+      <c r="G17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$D$17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="76">
+      <c r="H17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),'Results'!$B$17*'Results'!$E$17,0)</f>
         <v/>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$D$17,0)</f>
         <v/>
       </c>
-      <c r="K17" s="76">
+      <c r="K17" s="75">
         <f>IF(ISNUMBER('Results'!$B$17),15*'Results'!$E$17,0)</f>
         <v/>
       </c>
@@ -6824,7 +6908,7 @@
           <t>Nutrient cycling</t>
         </is>
       </c>
-      <c r="B18" s="76">
+      <c r="B18" s="75">
         <f>IF(COUNT('DEEP Score'!G38:G39)=0,"",SUM('DEEP Score'!G38:G39)/COUNT('DEEP Score'!G38:G39)*15)</f>
         <v/>
       </c>
@@ -6837,27 +6921,27 @@
       <c r="E18" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$D$18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),'Results'!$B$18*'Results'!$E$18,0)</f>
         <v/>
       </c>
-      <c r="I18" s="76">
+      <c r="I18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="J18" s="76">
+      <c r="J18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$D$18,0)</f>
         <v/>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="75">
         <f>IF(ISNUMBER('Results'!$B$18),15*'Results'!$E$18,0)</f>
         <v/>
       </c>
@@ -6868,7 +6952,7 @@
           <t>Water &amp; soil quality</t>
         </is>
       </c>
-      <c r="B19" s="76">
+      <c r="B19" s="75">
         <f>IF(COUNT('DEEP Score'!G40:G42)=0,"",SUM('DEEP Score'!G40:G42)/COUNT('DEEP Score'!G40:G42)*15)</f>
         <v/>
       </c>
@@ -6881,27 +6965,27 @@
       <c r="E19" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$D$19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$E$19,0)</f>
         <v/>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="J19" s="76">
+      <c r="J19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$D$19,0)</f>
         <v/>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="75">
         <f>IF(ISNUMBER('Results'!$B$19),15*'Results'!$E$19,0)</f>
         <v/>
       </c>
@@ -6912,7 +6996,7 @@
           <t>Habitat provision</t>
         </is>
       </c>
-      <c r="B20" s="76">
+      <c r="B20" s="75">
         <f>IF(COUNT('DEEP Score'!G43:G44)=0,"",SUM('DEEP Score'!G43:G44)/COUNT('DEEP Score'!G43:G44)*15)</f>
         <v/>
       </c>
@@ -6925,27 +7009,27 @@
       <c r="E20" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),'Results'!$B$20*'Results'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),'Results'!$B$20*'Results'!$D$20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),'Results'!$B$20*'Results'!$E$20,0)</f>
         <v/>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),15*'Results'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="J20" s="76">
+      <c r="J20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),15*'Results'!$D$20,0)</f>
         <v/>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="75">
         <f>IF(ISNUMBER('Results'!$B$20),15*'Results'!$E$20,0)</f>
         <v/>
       </c>
@@ -6956,8 +7040,8 @@
           <t>Population support</t>
         </is>
       </c>
-      <c r="B21" s="76">
-        <f>IF(COUNT('DEEP Score'!G45:G45)=0,"",SUM('DEEP Score'!G45:G45)/COUNT('DEEP Score'!G45:G45)*15)</f>
+      <c r="B21" s="75">
+        <f>IF(COUNT('DEEP Score'!G45:G46)=0,"",SUM('DEEP Score'!G45:G46)/COUNT('DEEP Score'!G45:G46)*15)</f>
         <v/>
       </c>
       <c r="C21" s="41" t="n">
@@ -6969,27 +7053,27 @@
       <c r="E21" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="76">
+      <c r="F21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),'Results'!$B$21*'Results'!$C$21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),'Results'!$B$21*'Results'!$D$21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="76">
+      <c r="H21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),'Results'!$B$21*'Results'!$E$21,0)</f>
         <v/>
       </c>
-      <c r="I21" s="76">
+      <c r="I21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),15*'Results'!$C$21,0)</f>
         <v/>
       </c>
-      <c r="J21" s="76">
+      <c r="J21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),15*'Results'!$D$21,0)</f>
         <v/>
       </c>
-      <c r="K21" s="76">
+      <c r="K21" s="75">
         <f>IF(ISNUMBER('Results'!$B$21),15*'Results'!$E$21,0)</f>
         <v/>
       </c>
@@ -7000,8 +7084,8 @@
           <t>Community dynamics</t>
         </is>
       </c>
-      <c r="B22" s="76">
-        <f>IF(COUNT('DEEP Score'!G46:G47)=0,"",SUM('DEEP Score'!G46:G47)/COUNT('DEEP Score'!G46:G47)*15)</f>
+      <c r="B22" s="75">
+        <f>IF(COUNT('DEEP Score'!G47:G48)=0,"",SUM('DEEP Score'!G47:G48)/COUNT('DEEP Score'!G47:G48)*15)</f>
         <v/>
       </c>
       <c r="C22" s="41" t="n">
@@ -7013,27 +7097,27 @@
       <c r="E22" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="76">
+      <c r="F22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),'Results'!$B$22*'Results'!$C$22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="76">
+      <c r="G22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),'Results'!$B$22*'Results'!$D$22,0)</f>
         <v/>
       </c>
-      <c r="H22" s="76">
+      <c r="H22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),'Results'!$B$22*'Results'!$E$22,0)</f>
         <v/>
       </c>
-      <c r="I22" s="76">
+      <c r="I22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),15*'Results'!$C$22,0)</f>
         <v/>
       </c>
-      <c r="J22" s="76">
+      <c r="J22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),15*'Results'!$D$22,0)</f>
         <v/>
       </c>
-      <c r="K22" s="76">
+      <c r="K22" s="75">
         <f>IF(ISNUMBER('Results'!$B$22),15*'Results'!$E$22,0)</f>
         <v/>
       </c>
@@ -7044,8 +7128,8 @@
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="B23" s="76">
-        <f>IF(COUNT('DEEP Score'!G48:G48)=0,"",SUM('DEEP Score'!G48:G48)/COUNT('DEEP Score'!G48:G48)*15)</f>
+      <c r="B23" s="75">
+        <f>IF(COUNT('DEEP Score'!G49:G49)=0,"",SUM('DEEP Score'!G49:G49)/COUNT('DEEP Score'!G49:G49)*15)</f>
         <v/>
       </c>
       <c r="C23" s="41" t="n">
@@ -7057,27 +7141,27 @@
       <c r="E23" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$C$23,0)</f>
         <v/>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$D$23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="76">
+      <c r="H23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$E$23,0)</f>
         <v/>
       </c>
-      <c r="I23" s="76">
+      <c r="I23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$C$23,0)</f>
         <v/>
       </c>
-      <c r="J23" s="76">
+      <c r="J23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$D$23,0)</f>
         <v/>
       </c>
-      <c r="K23" s="76">
+      <c r="K23" s="75">
         <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$E$23,0)</f>
         <v/>
       </c>
@@ -7100,7 +7184,7 @@
           <t>Physical</t>
         </is>
       </c>
-      <c r="B26" s="76">
+      <c r="B26" s="75">
         <f>IF(SUM('Results'!$I$4:$I$23)=0,0,SUM('Results'!$F$4:$F$23)/SUM('Results'!$I$4:$I$23))</f>
         <v/>
       </c>
@@ -7111,7 +7195,7 @@
           <t>Chemical</t>
         </is>
       </c>
-      <c r="B27" s="76">
+      <c r="B27" s="75">
         <f>IF(SUM('Results'!$J$4:$J$23)=0,0,SUM('Results'!$G$4:$G$23)/SUM('Results'!$J$4:$J$23))</f>
         <v/>
       </c>
@@ -7122,7 +7206,7 @@
           <t>Biological</t>
         </is>
       </c>
-      <c r="B28" s="76">
+      <c r="B28" s="75">
         <f>IF(SUM('Results'!$K$4:$K$23)=0,0,SUM('Results'!$H$4:$H$23)/SUM('Results'!$K$4:$K$23))</f>
         <v/>
       </c>
@@ -7133,7 +7217,7 @@
           <t>Ecosystem Condition Index</t>
         </is>
       </c>
-      <c r="B29" s="76">
+      <c r="B29" s="75">
         <f>('Results'!$B$26+'Results'!$B$27+'Results'!$B$28)/3</f>
         <v/>
       </c>
@@ -7150,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -7161,7 +7245,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Reference curves, bands and weights</t>
         </is>
@@ -7308,7 +7392,7 @@
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G5" s="41" t="n">
@@ -7382,7 +7466,7 @@
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G6" s="41" t="n">
@@ -7460,7 +7544,7 @@
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G7" s="41" t="n">
@@ -7538,7 +7622,7 @@
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G8" s="41" t="n">
@@ -7616,7 +7700,7 @@
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G9" s="41" t="n">
@@ -7690,7 +7774,7 @@
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G10" s="41" t="n">
@@ -7764,7 +7848,7 @@
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G11" s="41" t="n">
@@ -7838,7 +7922,7 @@
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G12" s="41" t="n">
@@ -7916,7 +8000,7 @@
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G13" s="41" t="n">
@@ -7994,7 +8078,7 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G14" s="41" t="n">
@@ -8072,7 +8156,7 @@
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G15" s="41" t="n">
@@ -8150,7 +8234,7 @@
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>50 least-disturbed stations of this ecoregion</t>
+          <t>50 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G16" s="41" t="n">
@@ -8228,7 +8312,7 @@
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>50 least-disturbed stations of this ecoregion</t>
+          <t>50 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G17" s="41" t="n">
@@ -8306,7 +8390,7 @@
       </c>
       <c r="F18" s="41" t="inlineStr">
         <is>
-          <t>50 least-disturbed stations of this ecoregion</t>
+          <t>50 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G18" s="41" t="n">
@@ -8384,7 +8468,7 @@
       </c>
       <c r="F19" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G19" s="41" t="n">
@@ -8462,7 +8546,7 @@
       </c>
       <c r="F20" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G20" s="41" t="n">
@@ -8540,7 +8624,7 @@
       </c>
       <c r="F21" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G21" s="41" t="n">
@@ -8614,7 +8698,7 @@
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G22" s="41" t="n">
@@ -8688,7 +8772,7 @@
       </c>
       <c r="F23" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G23" s="41" t="n">
@@ -8762,7 +8846,7 @@
       </c>
       <c r="F24" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G24" s="41" t="n">
@@ -8836,7 +8920,7 @@
       </c>
       <c r="F25" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G25" s="41" t="n">
@@ -8914,7 +8998,7 @@
       </c>
       <c r="F26" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G26" s="41" t="n">
@@ -8992,7 +9076,7 @@
       </c>
       <c r="F27" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G27" s="41" t="n">
@@ -9070,7 +9154,7 @@
       </c>
       <c r="F28" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G28" s="41" t="n">
@@ -9125,17 +9209,17 @@
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>spring_phab_lsub_dmm|</t>
+          <t>spring_phab_lwdeqvolm100|</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>spring-phab-lsub-dmm</t>
+          <t>spring-phab-lwdeqvolm100</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Substrate size</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr"/>
@@ -9144,32 +9228,32 @@
       </c>
       <c r="F29" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>50 least-disturbed stations of this ecoregion</t>
         </is>
       </c>
       <c r="G29" s="41" t="n">
-        <v>-2.029253174861272</v>
+        <v>0</v>
       </c>
       <c r="H29" s="41" t="n">
-        <v>-0.848638226588567</v>
+        <v>0.05107829852827957</v>
       </c>
       <c r="I29" s="41" t="n">
-        <v>0.7255150377750397</v>
+        <v>0.1191826965659857</v>
       </c>
       <c r="J29" s="41" t="n">
-        <v>1.906129986047745</v>
+        <v>3.798735737800598</v>
       </c>
       <c r="K29" s="41" t="n">
-        <v>2.260314470529556</v>
+        <v>4.902601650170982</v>
       </c>
       <c r="L29" s="41" t="n">
-        <v>2.260314470529556</v>
+        <v>4.902601650170982</v>
       </c>
       <c r="M29" s="41" t="n">
-        <v>2.260314470529556</v>
+        <v>4.902601650170982</v>
       </c>
       <c r="N29" s="41" t="n">
-        <v>2.260314470529556</v>
+        <v>4.902601650170982</v>
       </c>
       <c r="O29" s="41" t="n">
         <v>0</v>
@@ -9199,17 +9283,17 @@
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
-          <t>spring_phab_lwdeqvolm100|</t>
+          <t>spring_phab_lsub_dmm|</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>spring-phab-lwdeqvolm100</t>
+          <t>spring-phab-lsub-dmm</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Substrate size</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr"/>
@@ -9218,32 +9302,32 @@
       </c>
       <c r="F30" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G30" s="41" t="n">
-        <v>0</v>
+        <v>-2.029253174861272</v>
       </c>
       <c r="H30" s="41" t="n">
-        <v>0.0357589279966695</v>
+        <v>-0.848638226588567</v>
       </c>
       <c r="I30" s="41" t="n">
-        <v>0.08343749865889549</v>
+        <v>0.7255150377750397</v>
       </c>
       <c r="J30" s="41" t="n">
-        <v>3.527048707008362</v>
+        <v>1.906129986047745</v>
       </c>
       <c r="K30" s="41" t="n">
-        <v>4.560132069513202</v>
+        <v>2.260314470529556</v>
       </c>
       <c r="L30" s="41" t="n">
-        <v>4.560132069513202</v>
+        <v>2.260314470529556</v>
       </c>
       <c r="M30" s="41" t="n">
-        <v>4.560132069513202</v>
+        <v>2.260314470529556</v>
       </c>
       <c r="N30" s="41" t="n">
-        <v>4.560132069513202</v>
+        <v>2.260314470529556</v>
       </c>
       <c r="O30" s="41" t="n">
         <v>0</v>
@@ -9296,28 +9380,28 @@
         </is>
       </c>
       <c r="G31" s="41" t="n">
-        <v>0.07216500565409661</v>
+        <v>0.04717499278485776</v>
       </c>
       <c r="H31" s="41" t="n">
-        <v>0.3145500048995018</v>
+        <v>0.2407499961555004</v>
       </c>
       <c r="I31" s="41" t="n">
-        <v>1.122500002384186</v>
+        <v>0.886000007390976</v>
       </c>
       <c r="J31" s="41" t="n">
-        <v>2.199766665697098</v>
+        <v>1.746333355704943</v>
       </c>
       <c r="K31" s="41" t="n">
-        <v>3.007716663181782</v>
+        <v>2.391583366940419</v>
       </c>
       <c r="L31" s="41" t="n">
-        <v>3.007716663181782</v>
+        <v>2.391583366940419</v>
       </c>
       <c r="M31" s="41" t="n">
-        <v>3.007716663181782</v>
+        <v>2.391583366940419</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>3.007716663181782</v>
+        <v>2.391583366940419</v>
       </c>
       <c r="O31" s="41" t="n">
         <v>1</v>
@@ -9370,7 +9454,7 @@
       </c>
       <c r="F32" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G32" s="41" t="n">
@@ -9448,7 +9532,7 @@
       </c>
       <c r="F33" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G33" s="41" t="n">
@@ -9526,7 +9610,7 @@
       </c>
       <c r="F34" s="41" t="inlineStr">
         <is>
-          <t>63 least-disturbed stations of this ecoregion</t>
+          <t>63 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G34" s="41" t="n">
@@ -9600,7 +9684,7 @@
       </c>
       <c r="F35" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G35" s="41" t="n">
@@ -9674,7 +9758,7 @@
       </c>
       <c r="F36" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G36" s="41" t="n">
@@ -9748,7 +9832,7 @@
       </c>
       <c r="F37" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G37" s="41" t="n">
@@ -9822,7 +9906,7 @@
       </c>
       <c r="F38" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G38" s="41" t="n">
@@ -9896,7 +9980,7 @@
       </c>
       <c r="F39" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G39" s="41" t="n">
@@ -9970,7 +10054,7 @@
       </c>
       <c r="F40" s="41" t="inlineStr">
         <is>
-          <t>62 least-disturbed stations of this ecoregion</t>
+          <t>62 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G40" s="41" t="n">
@@ -10048,7 +10132,7 @@
       </c>
       <c r="F41" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G41" s="41" t="n">
@@ -10126,7 +10210,7 @@
       </c>
       <c r="F42" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G42" s="41" t="n">
@@ -10204,7 +10288,7 @@
       </c>
       <c r="F43" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G43" s="41" t="n">
@@ -10282,7 +10366,7 @@
       </c>
       <c r="F44" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G44" s="41" t="n">
@@ -10360,7 +10444,7 @@
       </c>
       <c r="F45" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G45" s="41" t="n">
@@ -10438,7 +10522,7 @@
       </c>
       <c r="F46" s="41" t="inlineStr">
         <is>
-          <t>66 least-disturbed stations of this ecoregion</t>
+          <t>66 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G46" s="41" t="n">
@@ -10493,55 +10577,51 @@
     <row r="47">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>spring_fish_nat_totlntax|All streams (pooled)</t>
+          <t>spring_bent_totlntax|</t>
         </is>
       </c>
       <c r="B47" s="41" t="inlineStr">
         <is>
-          <t>spring-fish-nat-totlntax</t>
+          <t>spring-bent-totlntax</t>
         </is>
       </c>
       <c r="C47" s="41" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
-        </is>
-      </c>
-      <c r="D47" s="41" t="inlineStr">
-        <is>
-          <t>All streams (pooled)</t>
-        </is>
-      </c>
+          <t>Benthic total taxa richness</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr"/>
       <c r="E47" s="41" t="n">
         <v>5</v>
       </c>
       <c r="F47" s="41" t="inlineStr">
         <is>
-          <t>64 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion</t>
         </is>
       </c>
       <c r="G47" s="41" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="41" t="n">
-        <v>0.4285714285714285</v>
+        <v>14.14285714285714</v>
       </c>
       <c r="I47" s="41" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J47" s="41" t="n">
-        <v>5.25</v>
+        <v>47</v>
       </c>
       <c r="K47" s="41" t="n">
-        <v>6.525</v>
+        <v>51.2</v>
       </c>
       <c r="L47" s="41" t="n">
-        <v>6.525</v>
+        <v>51.2</v>
       </c>
       <c r="M47" s="41" t="n">
-        <v>6.525</v>
+        <v>51.2</v>
       </c>
       <c r="N47" s="41" t="n">
-        <v>6.525</v>
+        <v>51.2</v>
       </c>
       <c r="O47" s="41" t="n">
         <v>0</v>
@@ -10571,7 +10651,7 @@
     <row r="48">
       <c r="A48" s="41" t="inlineStr">
         <is>
-          <t>spring_fish_nat_totlntax|Moderate gradient (0.5 to 2 percent)</t>
+          <t>spring_fish_nat_totlntax|All streams (pooled)</t>
         </is>
       </c>
       <c r="B48" s="41" t="inlineStr">
@@ -10586,7 +10666,7 @@
       </c>
       <c r="D48" s="41" t="inlineStr">
         <is>
-          <t>Moderate gradient (0.5 to 2 percent)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="E48" s="41" t="n">
@@ -10594,32 +10674,32 @@
       </c>
       <c r="F48" s="41" t="inlineStr">
         <is>
-          <t>64 least-disturbed stations of this ecoregion</t>
+          <t>64 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G48" s="41" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="41" t="n">
-        <v>1.285714285714286</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I48" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" s="41" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="K48" s="41" t="n">
-        <v>7.55</v>
+        <v>6.525</v>
       </c>
       <c r="L48" s="41" t="n">
-        <v>7.55</v>
+        <v>6.525</v>
       </c>
       <c r="M48" s="41" t="n">
-        <v>7.55</v>
+        <v>6.525</v>
       </c>
       <c r="N48" s="41" t="n">
-        <v>7.55</v>
+        <v>6.525</v>
       </c>
       <c r="O48" s="41" t="n">
         <v>0</v>
@@ -10649,7 +10729,7 @@
     <row r="49">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>spring_fish_nat_totlntax|Steep (2 percent and above)</t>
+          <t>spring_fish_nat_totlntax|Moderate gradient (0.5 to 2 percent)</t>
         </is>
       </c>
       <c r="B49" s="41" t="inlineStr">
@@ -10664,7 +10744,7 @@
       </c>
       <c r="D49" s="41" t="inlineStr">
         <is>
-          <t>Steep (2 percent and above)</t>
+          <t>Moderate gradient (0.5 to 2 percent)</t>
         </is>
       </c>
       <c r="E49" s="41" t="n">
@@ -10672,32 +10752,32 @@
       </c>
       <c r="F49" s="41" t="inlineStr">
         <is>
-          <t>64 least-disturbed stations of this ecoregion</t>
+          <t>64 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G49" s="41" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="41" t="n">
-        <v>0.4285714285714285</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="I49" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" s="41" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="K49" s="41" t="n">
-        <v>3.6</v>
+        <v>7.55</v>
       </c>
       <c r="L49" s="41" t="n">
-        <v>3.6</v>
+        <v>7.55</v>
       </c>
       <c r="M49" s="41" t="n">
-        <v>3.6</v>
+        <v>7.55</v>
       </c>
       <c r="N49" s="41" t="n">
-        <v>3.6</v>
+        <v>7.55</v>
       </c>
       <c r="O49" s="41" t="n">
         <v>0</v>
@@ -10727,51 +10807,55 @@
     <row r="50">
       <c r="A50" s="41" t="inlineStr">
         <is>
-          <t>spring_bent_ept_ntax|</t>
+          <t>spring_fish_nat_totlntax|Steep (2 percent and above)</t>
         </is>
       </c>
       <c r="B50" s="41" t="inlineStr">
         <is>
-          <t>spring-bent-ept-ntax</t>
+          <t>spring-fish-nat-totlntax</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
-        </is>
-      </c>
-      <c r="D50" s="41" t="inlineStr"/>
+          <t>Native fish taxa richness</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>Steep (2 percent and above)</t>
+        </is>
+      </c>
       <c r="E50" s="41" t="n">
         <v>5</v>
       </c>
       <c r="F50" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>64 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G50" s="41" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="41" t="n">
-        <v>4.714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I50" s="41" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J50" s="41" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K50" s="41" t="n">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="L50" s="41" t="n">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="M50" s="41" t="n">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="N50" s="41" t="n">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="O50" s="41" t="n">
         <v>0</v>
@@ -10801,17 +10885,17 @@
     <row r="51">
       <c r="A51" s="41" t="inlineStr">
         <is>
-          <t>spring_bent_hprime|</t>
+          <t>spring_bent_ept_ntax|</t>
         </is>
       </c>
       <c r="B51" s="41" t="inlineStr">
         <is>
-          <t>spring-bent-hprime</t>
+          <t>spring-bent-ept-ntax</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr"/>
@@ -10820,32 +10904,32 @@
       </c>
       <c r="F51" s="41" t="inlineStr">
         <is>
-          <t>65 least-disturbed stations of this ecoregion</t>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
         </is>
       </c>
       <c r="G51" s="41" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="41" t="n">
-        <v>1.152857167380197</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="I51" s="41" t="n">
-        <v>2.690000057220459</v>
+        <v>11</v>
       </c>
       <c r="J51" s="41" t="n">
-        <v>3.130000114440918</v>
+        <v>21</v>
       </c>
       <c r="K51" s="41" t="n">
-        <v>3.262000131607055</v>
+        <v>24</v>
       </c>
       <c r="L51" s="41" t="n">
-        <v>3.262000131607055</v>
+        <v>24</v>
       </c>
       <c r="M51" s="41" t="n">
-        <v>3.262000131607055</v>
+        <v>24</v>
       </c>
       <c r="N51" s="41" t="n">
-        <v>3.262000131607055</v>
+        <v>24</v>
       </c>
       <c r="O51" s="41" t="n">
         <v>0</v>
@@ -10875,100 +10959,162 @@
     <row r="52">
       <c r="A52" s="41" t="inlineStr">
         <is>
-          <t>spring_nid_dams_1mi|</t>
+          <t>spring_bent_hprime|</t>
         </is>
       </c>
       <c r="B52" s="41" t="inlineStr">
         <is>
-          <t>spring-nid-dams-1mi</t>
+          <t>spring-bent-hprime</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>Mapped dams within one mile</t>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr"/>
       <c r="E52" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="41" t="inlineStr">
+        <is>
+          <t>65 least-disturbed stations of this ecoregion, carried forward from version 8</t>
+        </is>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="41" t="n">
+        <v>1.152857167380197</v>
+      </c>
+      <c r="I52" s="41" t="n">
+        <v>2.690000057220459</v>
+      </c>
+      <c r="J52" s="41" t="n">
+        <v>3.130000114440918</v>
+      </c>
+      <c r="K52" s="41" t="n">
+        <v>3.262000131607055</v>
+      </c>
+      <c r="L52" s="41" t="n">
+        <v>3.262000131607055</v>
+      </c>
+      <c r="M52" s="41" t="n">
+        <v>3.262000131607055</v>
+      </c>
+      <c r="N52" s="41" t="n">
+        <v>3.262000131607055</v>
+      </c>
+      <c r="O52" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q52" s="41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R52" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" s="41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>spring_nid_dams_1mi|</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
+        <is>
+          <t>spring-nid-dams-1mi</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr"/>
+      <c r="E53" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="41" t="inlineStr">
-        <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
-        </is>
-      </c>
-      <c r="G52" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="41" t="n">
+      <c r="F53" s="41" t="inlineStr">
+        <is>
+          <t>Fixed criteria, the same in every region</t>
+        </is>
+      </c>
+      <c r="G53" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="41" t="n">
+      <c r="J53" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="K52" s="41" t="n">
+      <c r="K53" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="L52" s="41" t="n">
+      <c r="L53" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="M52" s="41" t="n">
+      <c r="M53" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="N52" s="41" t="n">
+      <c r="N53" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="O52" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" s="41" t="n">
+      <c r="O53" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="41" t="n">
         <v>0.545</v>
       </c>
-      <c r="Q52" s="41" t="n">
+      <c r="Q53" s="41" t="n">
         <v>0.195</v>
       </c>
-      <c r="R52" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="65" t="inlineStr">
+      <c r="R53" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="77" t="inlineStr">
         <is>
           <t>Curve sets by metric</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="41" t="inlineStr">
-        <is>
-          <t>All streams (pooled)</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Wetland</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="41" t="inlineStr">
         <is>
-          <t>Moderate gradient (0.5 to 2 percent)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -10980,7 +11126,7 @@
     <row r="58">
       <c r="A58" s="41" t="inlineStr">
         <is>
-          <t>Steep (2 percent and above)</t>
+          <t>Moderate gradient (0.5 to 2 percent)</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -10992,19 +11138,19 @@
     <row r="59">
       <c r="A59" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Steep (2 percent and above)</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Bankfull width:depth ratio</t>
+          <t>Wetland</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="41" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -11016,7 +11162,7 @@
     <row r="61">
       <c r="A61" s="41" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -11028,19 +11174,19 @@
     <row r="62">
       <c r="A62" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Residual pool depth</t>
+          <t>Bankfull width:depth ratio</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="41" t="inlineStr">
         <is>
-          <t>Moderate gradient (0.5 to 2 percent)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -11052,7 +11198,7 @@
     <row r="64">
       <c r="A64" s="41" t="inlineStr">
         <is>
-          <t>Steep (2 percent and above)</t>
+          <t>Moderate gradient (0.5 to 2 percent)</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -11064,19 +11210,19 @@
     <row r="65">
       <c r="A65" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Steep (2 percent and above)</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Bankfull height above channel</t>
+          <t>Residual pool depth</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -11088,7 +11234,7 @@
     <row r="67">
       <c r="A67" s="41" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -11100,19 +11246,19 @@
     <row r="68">
       <c r="A68" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Relative bed stability</t>
+          <t>Bankfull height above channel</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="41" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -11124,7 +11270,7 @@
     <row r="70">
       <c r="A70" s="41" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -11136,19 +11282,19 @@
     <row r="71">
       <c r="A71" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Canopy density, mid-channel</t>
+          <t>Relative bed stability</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="41" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -11160,7 +11306,7 @@
     <row r="73">
       <c r="A73" s="41" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -11172,19 +11318,19 @@
     <row r="74">
       <c r="A74" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Fast-water / riffle habitat</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="inlineStr">
         <is>
-          <t>Moderate gradient (0.5 to 2 percent)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -11196,7 +11342,7 @@
     <row r="76">
       <c r="A76" s="41" t="inlineStr">
         <is>
-          <t>Steep (2 percent and above)</t>
+          <t>Moderate gradient (0.5 to 2 percent)</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -11208,19 +11354,19 @@
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Steep (2 percent and above)</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Natural fish cover</t>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -11232,7 +11378,7 @@
     <row r="79">
       <c r="A79" s="41" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -11244,19 +11390,19 @@
     <row r="80">
       <c r="A80" s="41" t="inlineStr">
         <is>
-          <t>All streams (pooled)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
+          <t>Natural fish cover</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="41" t="inlineStr">
         <is>
-          <t>Moderate gradient (0.5 to 2 percent)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -11268,38 +11414,50 @@
     <row r="82">
       <c r="A82" s="41" t="inlineStr">
         <is>
+          <t>Moderate gradient (0.5 to 2 percent)</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Native fish taxa richness</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="41" t="inlineStr">
+        <is>
           <t>Steep (2 percent and above)</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Native fish taxa richness</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="65" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="77" t="inlineStr">
         <is>
           <t>Condition classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
+        <is>
+          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Outcome weights: a direct contribution counts 1, an indirect one 0.1.</t>
         </is>
@@ -11325,7 +11483,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Metadata and version information</t>
         </is>
@@ -11374,7 +11532,7 @@
         </is>
       </c>
       <c r="B6" s="41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -11393,7 +11551,7 @@
       </c>
       <c r="B8" s="41" t="inlineStr">
         <is>
-          <t>sha256:8b00cfe9b148157bdf3491a42e11723d98422db39c5d71a647b68eda88ece4a6</t>
+          <t>sha256:4902d33d13042a2aff1c22bf8ac22e615dcb53ce02507641cf290e61d23ce593</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11575,7 @@
       </c>
       <c r="B10" s="41" t="inlineStr">
         <is>
-          <t>USEPA NRSA 2013-24 (L3 ecoregion 58), StreamCurves regional analysis, methodology 0.13-provisional</t>
+          <t>USEPA NRSA 2013-24 (L3 ecoregion 58), StreamCurves regional analysis, methodology 0.14-provisional</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11632,7 @@
         </is>
       </c>
       <c r="B15" s="41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -11551,27 +11709,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>Non-Functioning (0-5)</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="77" t="inlineStr">
         <is>
           <t>Functioning At-Risk (6-10)</t>
         </is>
       </c>
-      <c r="E2" s="65" t="inlineStr">
+      <c r="E2" s="77" t="inlineStr">
         <is>
           <t>Functioning (11-15)</t>
         </is>
@@ -12038,27 +12196,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C24" s="65" t="inlineStr">
+      <c r="C24" s="77" t="inlineStr">
         <is>
           <t>Non-Functioning (0.00-0.39)</t>
         </is>
       </c>
-      <c r="D24" s="65" t="inlineStr">
+      <c r="D24" s="77" t="inlineStr">
         <is>
           <t>Functioning At-Risk (0.40-0.69)</t>
         </is>
       </c>
-      <c r="E24" s="65" t="inlineStr">
+      <c r="E24" s="77" t="inlineStr">
         <is>
           <t>Functioning (0.70-1.00)</t>
         </is>

--- a/apps/deep/www/calculators/northeastern-highlands.xlsx
+++ b/apps/deep/www/calculators/northeastern-highlands.xlsx
@@ -1517,7 +1517,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -1657,7 +1657,7 @@
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -3184,7 +3184,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -6882,7 +6882,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -6926,7 +6926,7 @@
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -10366,7 +10366,7 @@
     <row r="2" ht="21" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary. Not yet certified for use.</t>
+          <t>Assessment status: Preliminary. Reviewed and approved as Preliminary.</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
@@ -11192,7 +11192,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary. Not yet certified for use.</oddHeader>
+    <oddHeader>&amp;C&amp;"Calibri,Bold"&amp;KB45309Assessment status: Preliminary._x000a_Reviewed and approved as Preliminary.</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>
